--- a/Paired_sample_test/Results/GeneOntology/GeneOntology_down_regulated.xlsx
+++ b/Paired_sample_test/Results/GeneOntology/GeneOntology_down_regulated.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <si>
     <t xml:space="preserve">Term</t>
   </si>
@@ -56,6 +56,21 @@
     <t xml:space="preserve">FN1;SKAP1</t>
   </si>
   <si>
+    <t xml:space="preserve">Integrin-mediated Signaling Pathway (GO:0007229)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGA11;FN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell-matrix Adhesion (GO:0007160)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/116</t>
+  </si>
+  <si>
     <t xml:space="preserve">Neural Crest Cell Migration Involved in Autonomic Nervous System Development (GO:1901166)</t>
   </si>
   <si>
@@ -83,6 +98,12 @@
     <t xml:space="preserve">Positive Regulation of Adaptive Immune Response (GO:0002821)</t>
   </si>
   <si>
+    <t xml:space="preserve">Collagen-activated Signaling Pathway (GO:0038065)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGA11</t>
+  </si>
+  <si>
     <t xml:space="preserve">Enteric Nervous System Development (GO:0048484)</t>
   </si>
   <si>
@@ -110,6 +131,12 @@
     <t xml:space="preserve">1/13</t>
   </si>
   <si>
+    <t xml:space="preserve">Substrate-dependent Cell Migration (GO:0006929)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Regulation of Integrin Activation (GO:0033623)</t>
   </si>
   <si>
@@ -233,148 +260,139 @@
     <t xml:space="preserve">1/48</t>
   </si>
   <si>
+    <t xml:space="preserve">Positive Regulation of Cell-Cell Adhesion (GO:0022409)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Leukocyte Cell-Cell Adhesion (GO:1903039)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muscle Organ Development (GO:0007517)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Cell-Matrix Adhesion (GO:0001952)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of T Cell Activation (GO:0050863)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T Cell Receptor Signaling Pathway (GO:0050852)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Protein Phosphorylation (GO:0001932)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Immune Response (GO:0050778)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Protein-Containing Complex Assembly (GO:0031334)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell Junction Assembly (GO:0034329)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antigen Receptor-Mediated Signaling Pathway (GO:0050851)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circulatory System Development (GO:0072359)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pos Reg Phosphatidylinositol 3-Kinase/Protein Kinase B Signal Transduction (GO:0051897)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heart Development (GO:0007507)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative Regulation of Cytokine Production (GO:0001818)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of ERK1 and ERK2 Cascade (GO:0070372)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Phosphatidylinositol 3-Kinase/Protein Kinase B Signal Transduction (GO:0051896)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of MAPK Cascade (GO:0043408)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein-containing Complex Assembly (GO:0065003)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Macromolecule Biosynthetic Process (GO:0010557)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Cell Migration (GO:0030335)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Gene Expression (GO:0010628)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Cell Population Proliferation (GO:0008284)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/486</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nervous System Development (GO:0007399)</t>
   </si>
   <si>
-    <t xml:space="preserve">2/531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAMDC4;FN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Cell-Cell Adhesion (GO:0022409)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Leukocyte Cell-Cell Adhesion (GO:1903039)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Cell-Matrix Adhesion (GO:0001952)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of T Cell Activation (GO:0050863)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrin-mediated Signaling Pathway (GO:0007229)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T Cell Receptor Signaling Pathway (GO:0050852)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Protein Phosphorylation (GO:0001932)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Immune Response (GO:0050778)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Protein-Containing Complex Assembly (GO:0031334)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cell Junction Assembly (GO:0034329)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cell-matrix Adhesion (GO:0007160)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antigen Receptor-Mediated Signaling Pathway (GO:0050851)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circulatory System Development (GO:0072359)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pos Reg Phosphatidylinositol 3-Kinase/Protein Kinase B Signal Transduction (GO:0051897)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heart Development (GO:0007507)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative Regulation of Cytokine Production (GO:0001818)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of ERK1 and ERK2 Cascade (GO:0070372)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Phosphatidylinositol 3-Kinase/Protein Kinase B Signal Transduction (GO:0051896)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of MAPK Cascade (GO:0043408)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protein-containing Complex Assembly (GO:0065003)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Macromolecule Biosynthetic Process (GO:0010557)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Cell Migration (GO:0030335)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Gene Expression (GO:0010628)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Cell Population Proliferation (GO:0008284)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/486</t>
+    <t xml:space="preserve">1/531</t>
   </si>
   <si>
     <t xml:space="preserve">Positive Regulation of RNA Biosynthetic Process (GO:1902680)</t>
@@ -440,16 +458,19 @@
     <t xml:space="preserve">SIT1;SKAP1</t>
   </si>
   <si>
-    <t xml:space="preserve">Disulfide Oxidoreductase Activity (GO:0015036)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXNL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single-stranded RNA Binding (GO:0003727)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZFR2</t>
+    <t xml:space="preserve">Collagen Receptor Activity (GO:0038064)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collagen Binding Involved in Cell-Matrix Adhesion (GO:0098639)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell-matrix Adhesion Mediator Activity (GO:0098634)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinase Binding (GO:0019900)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/467</t>
   </si>
   <si>
     <t xml:space="preserve">SH3 Domain Binding (GO:0017124)</t>
@@ -458,18 +479,6 @@
     <t xml:space="preserve">1/50</t>
   </si>
   <si>
-    <t xml:space="preserve">Kinase Binding (GO:0019900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Double-stranded RNA Binding (GO:0003725)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/71</t>
-  </si>
-  <si>
     <t xml:space="preserve">Phosphatase Binding (GO:0019902)</t>
   </si>
   <si>
@@ -485,10 +494,28 @@
     <t xml:space="preserve">Protein Phosphatase Binding (GO:0019903)</t>
   </si>
   <si>
+    <t xml:space="preserve">GTP Binding (GO:0005525)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBB8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guanyl Ribonucleotide Binding (GO:0032561)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/230</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protein Kinase Binding (GO:0019901)</t>
   </si>
   <si>
-    <t xml:space="preserve">1/531</t>
+    <t xml:space="preserve">Endoplasmic Reticulum Lumen (GO:0005788)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL26A1;FN1</t>
   </si>
   <si>
     <t xml:space="preserve">Supramolecular Fiber (GO:0099512)</t>
@@ -503,82 +530,139 @@
     <t xml:space="preserve">1/67</t>
   </si>
   <si>
-    <t xml:space="preserve">Acrosomal Vesicle (GO:0001669)</t>
+    <t xml:space="preserve">Plasma Membrane Raft (GO:0044853)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platelet Alpha Granule (GO:0031091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extracellular Exosome (GO:0070062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/2059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIT1;FN1;TUBB8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intracellular Organelle Lumen (GO:0070013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extracellular Vesicle (GO:1903561)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/2082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membrane Raft (GO:0045121)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microtubule (GO:0005874)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polymeric Cytoskeletal Fiber (GO:0099513)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretory Granule Lumen (GO:0034774)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microtubule Cytoskeleton (GO:0015630)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focal Adhesion (GO:0005925)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell-substrate Junction (GO:0030055)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECM-RECEPTOR INTERACTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTEGRIN SIGNALING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOCAL ADHESION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGULATION OF ACTIN CYTOSKELETON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYTOSKELETON IN MUSCLE CELLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUMAN PAPILLOMAVIRUS INFECTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PI3K-AKT SIGNALING PATHWAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BACTERIAL INVASION OF EPITHELIAL CELLS</t>
   </si>
   <si>
     <t xml:space="preserve">1/78</t>
   </si>
   <si>
-    <t xml:space="preserve">ACRV1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endoplasmic Reticulum Lumen (GO:0005788)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL26A1;FN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plasma Membrane Raft (GO:0044853)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platelet Alpha Granule (GO:0031091)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intracellular Organelle Lumen (GO:0070013)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Membrane Raft (GO:0045121)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vesicle (GO:0031982)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretory Granule Lumen (GO:0034774)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extracellular Exosome (GO:0070062)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/2059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIT1;FN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extracellular Vesicle (GO:1903561)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/2082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACTERIAL INVASION OF EPITHELIAL CELLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECM-RECEPTOR INTERACTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/88</t>
+    <t xml:space="preserve">GAP JUNCTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARRHYTHMOGENIC RIGHT VENTRICULAR CARDIOMYOPATHY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/86</t>
   </si>
   <si>
     <t xml:space="preserve">SMALL CELL LUNG CANCER</t>
@@ -587,6 +671,12 @@
     <t xml:space="preserve">1/92</t>
   </si>
   <si>
+    <t xml:space="preserve">HYPERTROPHIC CARDIOMYOPATHY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/98</t>
+  </si>
+  <si>
     <t xml:space="preserve">AGE-RAGE SIGNALING PATHWAY IN DIABETIC COMPLICATIONS</t>
   </si>
   <si>
@@ -605,16 +695,28 @@
     <t xml:space="preserve">COL26A1</t>
   </si>
   <si>
+    <t xml:space="preserve">DILATED CARDIOMYOPATHY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/103</t>
+  </si>
+  <si>
     <t xml:space="preserve">YERSINIA INFECTION</t>
   </si>
   <si>
     <t xml:space="preserve">1/138</t>
   </si>
   <si>
-    <t xml:space="preserve">INTEGRIN SIGNALING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/153</t>
+    <t xml:space="preserve">PHAGOSOME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOTOR PROTEINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/190</t>
   </si>
   <si>
     <t xml:space="preserve">PROTEOGLYCANS IN CANCER</t>
@@ -623,10 +725,10 @@
     <t xml:space="preserve">1/197</t>
   </si>
   <si>
-    <t xml:space="preserve">FOCAL ADHESION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/199</t>
+    <t xml:space="preserve">PATHOGENIC ESCHERICHIA COLI INFECTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/198</t>
   </si>
   <si>
     <t xml:space="preserve">RAP1 SIGNALING PATHWAY</t>
@@ -635,28 +737,49 @@
     <t xml:space="preserve">1/210</t>
   </si>
   <si>
-    <t xml:space="preserve">REGULATION OF ACTIN CYTOSKELETON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYTOSKELETON IN MUSCLE CELLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUMAN PAPILLOMAVIRUS INFECTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PI3K-AKT SIGNALING PATHWAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/355</t>
+    <t xml:space="preserve">SALMONELLA INFECTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARKINSON DISEASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRION DISEASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGSF CAM SIGNALING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUNTINGTON DISEASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMYOTROPHIC LATERAL SCLEROSIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALZHEIMER DISEASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATHWAYS OF NEURODEGENERATION - MULTIPLE DISEASES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/469</t>
   </si>
   <si>
     <t xml:space="preserve">PATHWAYS IN CANCER</t>
@@ -998,7 +1121,7 @@
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="60.71" hidden="0" customWidth="1"/>
   </cols>
@@ -1043,25 +1166,25 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00035286890580878</v>
+        <v>0.000189920342634409</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023995085594997</v>
+        <v>0.00984822287821286</v>
       </c>
       <c r="E2" t="n">
-        <v>94.8666666666667</v>
+        <v>142.314285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>754.13440259815</v>
+        <v>1219.47771155407</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.25</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>1.61987769651845</v>
+        <v>2.00664213131124</v>
       </c>
       <c r="J2" t="s">
         <v>12</v>
@@ -1075,25 +1198,25 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00199856343165899</v>
+        <v>0.000277414728963742</v>
       </c>
       <c r="D3" t="n">
-        <v>0.030779247077537</v>
+        <v>0.00984822287821286</v>
       </c>
       <c r="E3" t="n">
-        <v>713.857142857143</v>
+        <v>117.111764705882</v>
       </c>
       <c r="F3" t="n">
-        <v>4436.8553176414</v>
+        <v>959.144996337308</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>1.51174200809357</v>
+        <v>2.00664213131124</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -1107,60 +1230,60 @@
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00279701502710506</v>
+        <v>0.000492704444715923</v>
       </c>
       <c r="D4" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0116606718582768</v>
       </c>
       <c r="E4" t="n">
-        <v>475.857142857143</v>
+        <v>87.1929824561404</v>
       </c>
       <c r="F4" t="n">
-        <v>2797.66050021554</v>
+        <v>664.026970255321</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>1.51174200809357</v>
+        <v>1.93327642591181</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="n">
+        <v>0.0014992198216207</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0195003019187619</v>
+      </c>
+      <c r="E5" t="n">
+        <v>999.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6499.55901988972</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.70995866450224</v>
+      </c>
+      <c r="J5" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.00359490866621763</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.030779247077537</v>
-      </c>
-      <c r="E5" t="n">
-        <v>356.857142857143</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2008.47646591344</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.51174200809357</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -1168,511 +1291,511 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00359490866621763</v>
+        <v>0.00209838728197325</v>
       </c>
       <c r="D6" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0195003019187619</v>
       </c>
       <c r="E6" t="n">
-        <v>356.857142857143</v>
+        <v>666.266666666667</v>
       </c>
       <c r="F6" t="n">
-        <v>2008.47646591344</v>
+        <v>4108.59082569121</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I6" t="n">
-        <v>1.51174200809357</v>
+        <v>1.70995866450224</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.00269725593591418</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0195003019187619</v>
+      </c>
+      <c r="E7" t="n">
+        <v>499.65</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2955.68973928353</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.70995866450224</v>
+      </c>
+      <c r="J7" t="s">
         <v>20</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.00359490866621763</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.030779247077537</v>
-      </c>
-      <c r="E7" t="n">
-        <v>356.857142857143</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2008.47646591344</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.51174200809357</v>
-      </c>
-      <c r="J7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.00269725593591418</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0195003019187619</v>
+      </c>
+      <c r="E8" t="n">
+        <v>499.65</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2955.68973928353</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.70995866450224</v>
+      </c>
+      <c r="J8" t="s">
         <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.00439224439616303</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.030779247077537</v>
-      </c>
-      <c r="E8" t="n">
-        <v>285.457142857143</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1549.43708775113</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.51174200809357</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
       <c r="C9" t="n">
-        <v>0.00439224439616303</v>
+        <v>0.00269725593591418</v>
       </c>
       <c r="D9" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0195003019187619</v>
       </c>
       <c r="E9" t="n">
-        <v>285.457142857143</v>
+        <v>499.65</v>
       </c>
       <c r="F9" t="n">
-        <v>1549.43708775113</v>
+        <v>2955.68973928353</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I9" t="n">
-        <v>1.51174200809357</v>
+        <v>1.70995866450224</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00439224439616303</v>
+        <v>0.00269725593591418</v>
       </c>
       <c r="D10" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0195003019187619</v>
       </c>
       <c r="E10" t="n">
-        <v>285.457142857143</v>
+        <v>499.65</v>
       </c>
       <c r="F10" t="n">
-        <v>1549.43708775113</v>
+        <v>2955.68973928353</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>1.51174200809357</v>
+        <v>1.70995866450224</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00479070309341298</v>
+        <v>0.00329582567641046</v>
       </c>
       <c r="D11" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0195003019187619</v>
       </c>
       <c r="E11" t="n">
-        <v>259.493506493507</v>
+        <v>399.68</v>
       </c>
       <c r="F11" t="n">
-        <v>1385.97508325908</v>
+        <v>2284.21059157039</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I11" t="n">
-        <v>1.51174200809357</v>
+        <v>1.70995866450224</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00518902237949986</v>
+        <v>0.00329582567641046</v>
       </c>
       <c r="D12" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0195003019187619</v>
       </c>
       <c r="E12" t="n">
-        <v>237.857142857143</v>
+        <v>399.68</v>
       </c>
       <c r="F12" t="n">
-        <v>1251.41637042065</v>
+        <v>2284.21059157039</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I12" t="n">
-        <v>1.51174200809357</v>
+        <v>1.70995866450224</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
         <v>31</v>
       </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
       <c r="C13" t="n">
-        <v>0.00598524283644591</v>
+        <v>0.00329582567641046</v>
       </c>
       <c r="D13" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0195003019187619</v>
       </c>
       <c r="E13" t="n">
-        <v>203.857142857143</v>
+        <v>399.68</v>
       </c>
       <c r="F13" t="n">
-        <v>1043.43429845216</v>
+        <v>2284.21059157039</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I13" t="n">
-        <v>1.51174200809357</v>
+        <v>1.70995866450224</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00678090602009761</v>
+        <v>0.00359499844647963</v>
       </c>
       <c r="D14" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0196342222846195</v>
       </c>
       <c r="E14" t="n">
-        <v>178.357142857143</v>
+        <v>363.327272727273</v>
       </c>
       <c r="F14" t="n">
-        <v>890.652175215938</v>
+        <v>2044.88281453851</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I14" t="n">
-        <v>1.51174200809357</v>
+        <v>1.70698629654215</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0071785287204102</v>
+        <v>0.00389409648539669</v>
       </c>
       <c r="D15" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0197486321759404</v>
       </c>
       <c r="E15" t="n">
-        <v>167.857142857143</v>
+        <v>333.033333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>828.65378226444</v>
+        <v>1847.7667100463</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I15" t="n">
-        <v>1.51174200809357</v>
+        <v>1.70446297897488</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0071785287204102</v>
+        <v>0.00419311979869468</v>
       </c>
       <c r="D16" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0198474337138215</v>
       </c>
       <c r="E16" t="n">
-        <v>167.857142857143</v>
+        <v>307.4</v>
       </c>
       <c r="F16" t="n">
-        <v>828.65378226444</v>
+        <v>1682.80296780194</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I16" t="n">
-        <v>1.51174200809357</v>
+        <v>1.70229563983173</v>
       </c>
       <c r="J16" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00757601220630419</v>
+        <v>0.00449206839321453</v>
       </c>
       <c r="D17" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0199335534948895</v>
       </c>
       <c r="E17" t="n">
-        <v>158.52380952381</v>
+        <v>285.428571428571</v>
       </c>
       <c r="F17" t="n">
-        <v>774.03503382755</v>
+        <v>1542.86759275583</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I17" t="n">
-        <v>1.51174200809357</v>
+        <v>1.70041527402117</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00837056168160556</v>
+        <v>0.00508974145357057</v>
       </c>
       <c r="D18" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0201358464035876</v>
       </c>
       <c r="E18" t="n">
-        <v>142.657142857143</v>
+        <v>249.725</v>
       </c>
       <c r="F18" t="n">
-        <v>682.334006028863</v>
+        <v>1318.67991590424</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I18" t="n">
-        <v>1.51174200809357</v>
+        <v>1.69603011024916</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0087676277457428</v>
+        <v>0.00538846593898824</v>
       </c>
       <c r="D19" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0201358464035876</v>
       </c>
       <c r="E19" t="n">
-        <v>135.857142857143</v>
+        <v>235.023529411765</v>
       </c>
       <c r="F19" t="n">
-        <v>643.513034914984</v>
+        <v>1227.6441242999</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I19" t="n">
-        <v>1.51174200809357</v>
+        <v>1.69603011024916</v>
       </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
         <v>45</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00956134271782716</v>
+        <v>0.00538846593898824</v>
       </c>
       <c r="D20" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0201358464035876</v>
       </c>
       <c r="E20" t="n">
-        <v>124.031055900621</v>
+        <v>235.023529411765</v>
       </c>
       <c r="F20" t="n">
-        <v>576.747772435402</v>
+        <v>1227.6441242999</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I20" t="n">
-        <v>1.51174200809357</v>
+        <v>1.69603011024916</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0099579917015561</v>
+        <v>0.00568711573898333</v>
       </c>
       <c r="D21" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0201892608733908</v>
       </c>
       <c r="E21" t="n">
-        <v>118.857142857143</v>
+        <v>221.955555555556</v>
       </c>
       <c r="F21" t="n">
-        <v>547.857720990995</v>
+        <v>1147.41079930952</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I21" t="n">
-        <v>1.51174200809357</v>
+        <v>1.69487958023831</v>
       </c>
       <c r="J21" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1680,639 +1803,639 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0099579917015561</v>
+        <v>0.00628419133253944</v>
       </c>
       <c r="D22" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0204191816738413</v>
       </c>
       <c r="E22" t="n">
-        <v>118.857142857143</v>
+        <v>199.74</v>
       </c>
       <c r="F22" t="n">
-        <v>547.857720990995</v>
+        <v>1012.62549558717</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I22" t="n">
-        <v>1.51174200809357</v>
+        <v>1.68996166683562</v>
       </c>
       <c r="J22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0099579917015561</v>
+        <v>0.00658261714792867</v>
       </c>
       <c r="D23" t="n">
-        <v>0.030779247077537</v>
+        <v>0.0204191816738413</v>
       </c>
       <c r="E23" t="n">
-        <v>118.857142857143</v>
+        <v>190.219047619048</v>
       </c>
       <c r="F23" t="n">
-        <v>547.857720990995</v>
+        <v>955.531692191046</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I23" t="n">
-        <v>1.51174200809357</v>
+        <v>1.68996166683562</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0115431985365685</v>
+        <v>0.0071792448741713</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0341277174124634</v>
+        <v>0.0204191816738413</v>
       </c>
       <c r="E24" t="n">
-        <v>101.857142857143</v>
+        <v>173.660869565217</v>
       </c>
       <c r="F24" t="n">
-        <v>454.451826608544</v>
+        <v>857.287488456765</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I24" t="n">
-        <v>1.46689275796579</v>
+        <v>1.68996166683562</v>
       </c>
       <c r="J24" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0123349690429112</v>
+        <v>0.00747744681013907</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0349490789549149</v>
+        <v>0.0204191816738413</v>
       </c>
       <c r="E25" t="n">
-        <v>95.0571428571429</v>
+        <v>166.416666666667</v>
       </c>
       <c r="F25" t="n">
-        <v>417.80627965005</v>
+        <v>814.753347497614</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I25" t="n">
-        <v>1.45656426512771</v>
+        <v>1.68996166683562</v>
       </c>
       <c r="J25" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
         <v>56</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0131261847028175</v>
+        <v>0.00747744681013907</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0353641442470695</v>
+        <v>0.0204191816738413</v>
       </c>
       <c r="E26" t="n">
-        <v>89.1071428571429</v>
+        <v>166.416666666667</v>
       </c>
       <c r="F26" t="n">
-        <v>386.114278489562</v>
+        <v>814.753347497614</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I26" t="n">
-        <v>1.45143684665186</v>
+        <v>1.68996166683562</v>
       </c>
       <c r="J26" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C27" t="n">
-        <v>0.013521584565056</v>
+        <v>0.00747744681013907</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0353641442470695</v>
+        <v>0.0204191816738413</v>
       </c>
       <c r="E27" t="n">
-        <v>86.4025974025974</v>
+        <v>166.416666666667</v>
       </c>
       <c r="F27" t="n">
-        <v>371.830814220732</v>
+        <v>814.753347497614</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I27" t="n">
-        <v>1.45143684665186</v>
+        <v>1.68996166683562</v>
       </c>
       <c r="J27" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0147069527624561</v>
+        <v>0.00866950866872135</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0357168852802504</v>
+        <v>0.0227975968696006</v>
       </c>
       <c r="E28" t="n">
-        <v>79.1904761904762</v>
+        <v>142.614285714286</v>
       </c>
       <c r="F28" t="n">
-        <v>334.139060567782</v>
+        <v>677.124522385392</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I28" t="n">
-        <v>1.44712642113232</v>
+        <v>1.64211093024854</v>
       </c>
       <c r="J28" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0147069527624561</v>
+        <v>0.00926509224971447</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0357168852802504</v>
+        <v>0.0234936267760617</v>
       </c>
       <c r="E29" t="n">
-        <v>79.1904761904762</v>
+        <v>133.093333333333</v>
       </c>
       <c r="F29" t="n">
-        <v>334.139060567782</v>
+        <v>623.076634648791</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I29" t="n">
-        <v>1.44712642113232</v>
+        <v>1.62904993480822</v>
       </c>
       <c r="J29" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0166797975569069</v>
+        <v>0.00986037774269364</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0369971465071827</v>
+        <v>0.024040384019274</v>
       </c>
       <c r="E30" t="n">
-        <v>69.5156794425087</v>
+        <v>124.7625</v>
       </c>
       <c r="F30" t="n">
-        <v>284.566397512524</v>
+        <v>576.306782745311</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I30" t="n">
-        <v>1.431831770635</v>
+        <v>1.61905859922672</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0170739515504477</v>
+        <v>0.0101579087405383</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0369971465071827</v>
+        <v>0.024040384019274</v>
       </c>
       <c r="E31" t="n">
-        <v>67.8571428571429</v>
+        <v>120.975757575758</v>
       </c>
       <c r="F31" t="n">
-        <v>276.192229579909</v>
+        <v>555.218564896445</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I31" t="n">
-        <v>1.431831770635</v>
+        <v>1.61905859922672</v>
       </c>
       <c r="J31" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01864918566892</v>
+        <v>0.0110500548998868</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0369971465071827</v>
+        <v>0.0245173093091238</v>
       </c>
       <c r="E32" t="n">
-        <v>61.944099378882</v>
+        <v>110.877777777778</v>
       </c>
       <c r="F32" t="n">
-        <v>246.658479823396</v>
+        <v>499.539856773497</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I32" t="n">
-        <v>1.431831770635</v>
+        <v>1.61052719387303</v>
       </c>
       <c r="J32" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01864918566892</v>
+        <v>0.0110500548998868</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0369971465071827</v>
+        <v>0.0245173093091238</v>
       </c>
       <c r="E33" t="n">
-        <v>61.944099378882</v>
+        <v>110.877777777778</v>
       </c>
       <c r="F33" t="n">
-        <v>246.658479823396</v>
+        <v>499.539856773497</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I33" t="n">
-        <v>1.431831770635</v>
+        <v>1.61052719387303</v>
       </c>
       <c r="J33" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01864918566892</v>
+        <v>0.0125354765664382</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0369971465071827</v>
+        <v>0.0267474349304824</v>
       </c>
       <c r="E34" t="n">
-        <v>61.944099378882</v>
+        <v>97.3317073170732</v>
       </c>
       <c r="F34" t="n">
-        <v>246.658479823396</v>
+        <v>426.234285540356</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I34" t="n">
-        <v>1.431831770635</v>
+        <v>1.57271786033252</v>
       </c>
       <c r="J34" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0190426489375205</v>
+        <v>0.0128323377374526</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0369971465071827</v>
+        <v>0.0267474349304824</v>
       </c>
       <c r="E35" t="n">
-        <v>60.6231003039514</v>
+        <v>95.0095238095238</v>
       </c>
       <c r="F35" t="n">
-        <v>240.132594562701</v>
+        <v>413.841239970083</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I35" t="n">
-        <v>1.431831770635</v>
+        <v>1.57271786033252</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0177166935480221</v>
+        <v>0.0140190390147642</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0369971465071827</v>
+        <v>0.0267474349304824</v>
       </c>
       <c r="E36" t="n">
-        <v>12.2640201638311</v>
+        <v>86.7304347826087</v>
       </c>
       <c r="F36" t="n">
-        <v>49.4638341302194</v>
+        <v>370.10816194385</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.25</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I36" t="n">
-        <v>1.431831770635</v>
+        <v>1.57271786033252</v>
       </c>
       <c r="J36" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
         <v>76</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0202222107748752</v>
+        <v>0.0140190390147642</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0371651441267977</v>
+        <v>0.0267474349304824</v>
       </c>
       <c r="E37" t="n">
-        <v>56.9771428571429</v>
+        <v>86.7304347826087</v>
       </c>
       <c r="F37" t="n">
-        <v>222.266337799251</v>
+        <v>370.10816194385</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I37" t="n">
-        <v>1.42986417865946</v>
+        <v>1.57271786033252</v>
       </c>
       <c r="J37" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
         <v>76</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0202222107748752</v>
+        <v>0.0140190390147642</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0371651441267977</v>
+        <v>0.0267474349304824</v>
       </c>
       <c r="E38" t="n">
-        <v>56.9771428571429</v>
+        <v>86.7304347826087</v>
       </c>
       <c r="F38" t="n">
-        <v>222.266337799251</v>
+        <v>370.10816194385</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I38" t="n">
-        <v>1.42986417865946</v>
+        <v>1.57271786033252</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0268829840764005</v>
+        <v>0.0143155285543427</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0481063925577693</v>
+        <v>0.0267474349304824</v>
       </c>
       <c r="E39" t="n">
-        <v>42.4840085287846</v>
+        <v>84.8808510638298</v>
       </c>
       <c r="F39" t="n">
-        <v>153.63329523077</v>
+        <v>360.43893024633</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I39" t="n">
-        <v>1.31779720911272</v>
+        <v>1.57271786033252</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0327272017891214</v>
+        <v>0.0152045515346865</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0570628133759041</v>
+        <v>0.0269880789740686</v>
       </c>
       <c r="E40" t="n">
-        <v>34.6864111498258</v>
+        <v>79.776</v>
       </c>
       <c r="F40" t="n">
-        <v>118.611871734907</v>
+        <v>333.955136289159</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I40" t="n">
-        <v>1.24364682006923</v>
+        <v>1.5688280276574</v>
       </c>
       <c r="J40" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" t="s">
         <v>82</v>
       </c>
-      <c r="B41" t="s">
-        <v>83</v>
-      </c>
       <c r="C41" t="n">
-        <v>0.0342804638132286</v>
+        <v>0.0152045515346865</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0582767884824887</v>
+        <v>0.0269880789740686</v>
       </c>
       <c r="E41" t="n">
-        <v>33.0664451827243</v>
+        <v>79.776</v>
       </c>
       <c r="F41" t="n">
-        <v>111.539060160258</v>
+        <v>333.955136289159</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I41" t="n">
-        <v>1.2345043893448</v>
+        <v>1.5688280276574</v>
       </c>
       <c r="J41" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42">
@@ -2323,28 +2446,28 @@
         <v>85</v>
       </c>
       <c r="C42" t="n">
-        <v>0.037380442146754</v>
+        <v>0.0178676130920248</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0619968308775432</v>
+        <v>0.0309414763300917</v>
       </c>
       <c r="E42" t="n">
-        <v>30.2401215805471</v>
+        <v>67.5762711864407</v>
       </c>
       <c r="F42" t="n">
-        <v>99.3874148810262</v>
+        <v>271.978646877106</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I42" t="n">
-        <v>1.20763050997872</v>
+        <v>1.50945896837692</v>
       </c>
       <c r="J42" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
@@ -2355,28 +2478,28 @@
         <v>87</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0396997087104848</v>
+        <v>0.020229739174506</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0637394427890858</v>
+        <v>0.0341978924140459</v>
       </c>
       <c r="E43" t="n">
-        <v>28.4171428571429</v>
+        <v>59.4835820895522</v>
       </c>
       <c r="F43" t="n">
-        <v>91.6853944819699</v>
+        <v>232.021750766537</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I43" t="n">
-        <v>1.19559173745286</v>
+        <v>1.4660006583051</v>
       </c>
       <c r="J43" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
@@ -2387,28 +2510,28 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0412431688635261</v>
+        <v>0.0246459677840751</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0637394427890858</v>
+        <v>0.0406945049457984</v>
       </c>
       <c r="E44" t="n">
-        <v>27.3186813186813</v>
+        <v>48.5658536585366</v>
       </c>
       <c r="F44" t="n">
-        <v>87.099326165868</v>
+        <v>179.846251021588</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I44" t="n">
-        <v>1.19559173745286</v>
+        <v>1.39046423040218</v>
       </c>
       <c r="J44" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
@@ -2416,127 +2539,127 @@
         <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0412431688635261</v>
+        <v>0.0281669971363706</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0637394427890858</v>
+        <v>0.0454512908336889</v>
       </c>
       <c r="E45" t="n">
-        <v>27.3186813186813</v>
+        <v>42.3404255319149</v>
       </c>
       <c r="F45" t="n">
-        <v>87.099326165868</v>
+        <v>151.13856507235</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I45" t="n">
-        <v>1.19559173745286</v>
+        <v>1.34245377814086</v>
       </c>
       <c r="J45" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0427844580072879</v>
+        <v>0.0299235360194532</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0646520698776795</v>
+        <v>0.0469704149346112</v>
       </c>
       <c r="E46" t="n">
-        <v>26.3015873015873</v>
+        <v>39.788</v>
       </c>
       <c r="F46" t="n">
-        <v>82.8915663187741</v>
+        <v>139.620466706137</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I46" t="n">
-        <v>1.1894175663433</v>
+        <v>1.32817560326116</v>
       </c>
       <c r="J46" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0454764979116999</v>
+        <v>0.0310930915764328</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0672261273477303</v>
+        <v>0.0469704149346112</v>
       </c>
       <c r="E47" t="n">
-        <v>24.6919254658385</v>
+        <v>38.25</v>
       </c>
       <c r="F47" t="n">
-        <v>76.31186768318</v>
+        <v>132.756937975663</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I47" t="n">
-        <v>1.17246190614753</v>
+        <v>1.32817560326116</v>
       </c>
       <c r="J47" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" t="s">
         <v>95</v>
       </c>
-      <c r="B48" t="s">
-        <v>96</v>
-      </c>
       <c r="C48" t="n">
-        <v>0.0470118302742274</v>
+        <v>0.0310930915764328</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0680171161414354</v>
+        <v>0.0469704149346112</v>
       </c>
       <c r="E48" t="n">
-        <v>23.8571428571429</v>
+        <v>38.25</v>
       </c>
       <c r="F48" t="n">
-        <v>72.9397788805927</v>
+        <v>132.756937975663</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I48" t="n">
-        <v>1.16738178567016</v>
+        <v>1.32817560326116</v>
       </c>
       <c r="J48" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
@@ -2547,28 +2670,28 @@
         <v>98</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0550369282195952</v>
+        <v>0.0322614719403215</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0779689816444265</v>
+        <v>0.0477200939117256</v>
       </c>
       <c r="E49" t="n">
-        <v>20.2571428571429</v>
+        <v>36.8259259259259</v>
       </c>
       <c r="F49" t="n">
-        <v>58.7406681681905</v>
+        <v>126.455868700302</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I49" t="n">
-        <v>1.10807813807757</v>
+        <v>1.32129871032223</v>
       </c>
       <c r="J49" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -2579,28 +2702,28 @@
         <v>100</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0671519530979639</v>
+        <v>0.0354684660279251</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0931904655237049</v>
+        <v>0.051393083428218</v>
       </c>
       <c r="E50" t="n">
-        <v>16.4617940199336</v>
+        <v>33.4033613445378</v>
       </c>
       <c r="F50" t="n">
-        <v>44.4599683621174</v>
+        <v>111.537539925918</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I50" t="n">
-        <v>1.03062851878615</v>
+        <v>1.28909532518916</v>
       </c>
       <c r="J50" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
@@ -2611,28 +2734,28 @@
         <v>102</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0697839237890214</v>
+        <v>0.0415663206424517</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0949061363530691</v>
+        <v>0.0590241753122814</v>
       </c>
       <c r="E51" t="n">
-        <v>15.8124501197127</v>
+        <v>28.3628571428571</v>
       </c>
       <c r="F51" t="n">
-        <v>42.0983020967207</v>
+        <v>90.2070755648637</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I51" t="n">
-        <v>1.02270570645448</v>
+        <v>1.22897007218363</v>
       </c>
       <c r="J51" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
@@ -2643,28 +2766,28 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0772680713380292</v>
+        <v>0.0507964976461815</v>
       </c>
       <c r="D52" t="n">
-        <v>0.103024095117372</v>
+        <v>0.0707166928015468</v>
       </c>
       <c r="E52" t="n">
-        <v>14.2089016511127</v>
+        <v>23.0488372093023</v>
       </c>
       <c r="F52" t="n">
-        <v>36.3815297451556</v>
+        <v>68.6838723883163</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I52" t="n">
-        <v>0.987061191287799</v>
+        <v>1.1504780581141</v>
       </c>
       <c r="J52" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
@@ -2675,28 +2798,28 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0880264908328034</v>
+        <v>0.0528056923384244</v>
       </c>
       <c r="D53" t="n">
-        <v>0.112939648615672</v>
+        <v>0.0721000799236179</v>
       </c>
       <c r="E53" t="n">
-        <v>12.3834586466165</v>
+        <v>22.1396648044693</v>
       </c>
       <c r="F53" t="n">
-        <v>30.0932592904541</v>
+        <v>65.1157714862158</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I53" t="n">
-        <v>0.947153567798998</v>
+        <v>1.14206425386078</v>
       </c>
       <c r="J53" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
@@ -2704,95 +2827,95 @@
         <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0880264908328034</v>
+        <v>0.0585267307609904</v>
       </c>
       <c r="D54" t="n">
-        <v>0.112939648615672</v>
+        <v>0.0784037336609494</v>
       </c>
       <c r="E54" t="n">
-        <v>12.3834586466165</v>
+        <v>19.894472361809</v>
       </c>
       <c r="F54" t="n">
-        <v>30.0932592904541</v>
+        <v>56.4659177521415</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I54" t="n">
-        <v>0.947153567798998</v>
+        <v>1.1056632553036</v>
       </c>
       <c r="J54" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>0.111020769576404</v>
+        <v>0.0667710686239844</v>
       </c>
       <c r="D55" t="n">
-        <v>0.139803932059175</v>
+        <v>0.0861953794964162</v>
       </c>
       <c r="E55" t="n">
-        <v>9.67157584683358</v>
+        <v>17.3385964912281</v>
       </c>
       <c r="F55" t="n">
-        <v>21.2584910558997</v>
+        <v>46.9266582025697</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I55" t="n">
-        <v>0.854480613657665</v>
+        <v>1.06451601390838</v>
       </c>
       <c r="J55" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" t="s">
         <v>110</v>
       </c>
-      <c r="B56" t="s">
-        <v>111</v>
-      </c>
       <c r="C56" t="n">
-        <v>0.12784324623835</v>
+        <v>0.0667710686239844</v>
       </c>
       <c r="D56" t="n">
-        <v>0.156741596889363</v>
+        <v>0.0861953794964162</v>
       </c>
       <c r="E56" t="n">
-        <v>8.30684699915469</v>
+        <v>17.3385964912281</v>
       </c>
       <c r="F56" t="n">
-        <v>17.0867722934379</v>
+        <v>46.9266582025697</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I56" t="n">
-        <v>0.804815732936824</v>
+        <v>1.06451601390838</v>
       </c>
       <c r="J56" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
@@ -2803,28 +2926,28 @@
         <v>113</v>
       </c>
       <c r="C57" t="n">
-        <v>0.129616369895488</v>
+        <v>0.0844740453220733</v>
       </c>
       <c r="D57" t="n">
-        <v>0.156741596889363</v>
+        <v>0.107101021747629</v>
       </c>
       <c r="E57" t="n">
-        <v>8.18367346938776</v>
+        <v>13.5415807560137</v>
       </c>
       <c r="F57" t="n">
-        <v>16.7206867967252</v>
+        <v>33.4654567722162</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I57" t="n">
-        <v>0.804815732936824</v>
+        <v>0.970206385963285</v>
       </c>
       <c r="J57" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -2835,28 +2958,28 @@
         <v>115</v>
       </c>
       <c r="C58" t="n">
-        <v>0.131386338569025</v>
+        <v>0.0974979888806524</v>
       </c>
       <c r="D58" t="n">
-        <v>0.156741596889363</v>
+        <v>0.120638655665644</v>
       </c>
       <c r="E58" t="n">
-        <v>8.064039408867</v>
+        <v>11.6307692307692</v>
       </c>
       <c r="F58" t="n">
-        <v>16.3668803990092</v>
+        <v>27.0755413416995</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I58" t="n">
-        <v>0.804815732936824</v>
+        <v>0.918513510998883</v>
       </c>
       <c r="J58" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
@@ -2867,28 +2990,28 @@
         <v>117</v>
       </c>
       <c r="C59" t="n">
-        <v>0.157560525915391</v>
+        <v>0.0988743811445363</v>
       </c>
       <c r="D59" t="n">
-        <v>0.184726133831838</v>
+        <v>0.120638655665644</v>
       </c>
       <c r="E59" t="n">
-        <v>6.60891590678825</v>
+        <v>11.4583090379009</v>
       </c>
       <c r="F59" t="n">
-        <v>12.2129170906203</v>
+        <v>26.5134398563218</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I59" t="n">
-        <v>0.733471659101857</v>
+        <v>0.918513510998883</v>
       </c>
       <c r="J59" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -2899,28 +3022,28 @@
         <v>119</v>
       </c>
       <c r="C60" t="n">
-        <v>0.178674127785297</v>
+        <v>0.100249023722155</v>
       </c>
       <c r="D60" t="n">
-        <v>0.205929503210173</v>
+        <v>0.120638655665644</v>
       </c>
       <c r="E60" t="n">
-        <v>5.74580265095729</v>
+        <v>11.2908045977011</v>
       </c>
       <c r="F60" t="n">
-        <v>9.89537333342662</v>
+        <v>25.9699565234215</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I60" t="n">
-        <v>0.686281428207237</v>
+        <v>0.918513510998883</v>
       </c>
       <c r="J60" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -2931,28 +3054,28 @@
         <v>121</v>
       </c>
       <c r="C61" t="n">
-        <v>0.203922587669778</v>
+        <v>0.120659906158221</v>
       </c>
       <c r="D61" t="n">
-        <v>0.231112266025748</v>
+        <v>0.142780888953895</v>
       </c>
       <c r="E61" t="n">
-        <v>4.94805194805195</v>
+        <v>9.25342789598109</v>
       </c>
       <c r="F61" t="n">
-        <v>7.86747597385955</v>
+        <v>19.5689585430409</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I61" t="n">
-        <v>0.636177004213964</v>
+        <v>0.845329918451319</v>
       </c>
       <c r="J61" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
@@ -2963,28 +3086,28 @@
         <v>123</v>
       </c>
       <c r="C62" t="n">
-        <v>0.231354084211128</v>
+        <v>0.137240211199119</v>
       </c>
       <c r="D62" t="n">
-        <v>0.257902913546831</v>
+        <v>0.159738606477663</v>
       </c>
       <c r="E62" t="n">
-        <v>4.2781954887218</v>
+        <v>8.04494845360825</v>
       </c>
       <c r="F62" t="n">
-        <v>6.26244784037877</v>
+        <v>15.9774488179155</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I62" t="n">
-        <v>0.588543751579921</v>
+        <v>0.796590108570764</v>
       </c>
       <c r="J62" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63">
@@ -2995,28 +3118,28 @@
         <v>125</v>
       </c>
       <c r="C63" t="n">
-        <v>0.25021607493981</v>
+        <v>0.149110432986687</v>
       </c>
       <c r="D63" t="n">
-        <v>0.274430533804953</v>
+        <v>0.170755495839594</v>
       </c>
       <c r="E63" t="n">
-        <v>3.90246863617968</v>
+        <v>7.34490566037736</v>
       </c>
       <c r="F63" t="n">
-        <v>5.4065988188406</v>
+        <v>13.9778555611783</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I63" t="n">
-        <v>0.56156756962247</v>
+        <v>0.767625309465474</v>
       </c>
       <c r="J63" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
@@ -3027,28 +3150,28 @@
         <v>127</v>
       </c>
       <c r="C64" t="n">
-        <v>0.271708804793599</v>
+        <v>0.15720826780119</v>
       </c>
       <c r="D64" t="n">
-        <v>0.293272995650234</v>
+        <v>0.177171222442611</v>
       </c>
       <c r="E64" t="n">
-        <v>3.53755522827688</v>
+        <v>6.92798573975045</v>
       </c>
       <c r="F64" t="n">
-        <v>4.6095206258566</v>
+        <v>12.818047025374</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I64" t="n">
-        <v>0.532727924677202</v>
+        <v>0.751606818280394</v>
       </c>
       <c r="J64" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
@@ -3059,28 +3182,28 @@
         <v>129</v>
       </c>
       <c r="C65" t="n">
-        <v>0.341917351004847</v>
+        <v>0.179083240474479</v>
       </c>
       <c r="D65" t="n">
-        <v>0.36328718544265</v>
+        <v>0.198670469901376</v>
       </c>
       <c r="E65" t="n">
-        <v>2.66264383946113</v>
+        <v>5.99009287925697</v>
       </c>
       <c r="F65" t="n">
-        <v>2.85751271682698</v>
+        <v>10.3023880018557</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I65" t="n">
-        <v>0.439749921129024</v>
+        <v>0.701866681012794</v>
       </c>
       <c r="J65" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
@@ -3091,28 +3214,28 @@
         <v>131</v>
       </c>
       <c r="C66" t="n">
-        <v>0.376334862732875</v>
+        <v>0.194237796726968</v>
       </c>
       <c r="D66" t="n">
-        <v>0.393704164089776</v>
+        <v>0.212167439501765</v>
       </c>
       <c r="E66" t="n">
-        <v>2.35146600124766</v>
+        <v>5.46402266288952</v>
       </c>
       <c r="F66" t="n">
-        <v>2.29803114571191</v>
+        <v>8.95374156914419</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I66" t="n">
-        <v>0.404829991784197</v>
+        <v>0.673321264778343</v>
       </c>
       <c r="J66" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67">
@@ -3123,28 +3246,28 @@
         <v>133</v>
       </c>
       <c r="C67" t="n">
-        <v>0.416947534402119</v>
+        <v>0.211622749515474</v>
       </c>
       <c r="D67" t="n">
-        <v>0.42958230817188</v>
+        <v>0.227654775993919</v>
       </c>
       <c r="E67" t="n">
-        <v>2.04900778423418</v>
+        <v>4.95309278350515</v>
       </c>
       <c r="F67" t="n">
-        <v>1.7924615225812</v>
+        <v>7.69190579917086</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I67" t="n">
-        <v>0.366953612833506</v>
+        <v>0.642723234149787</v>
       </c>
       <c r="J67" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68">
@@ -3155,28 +3278,28 @@
         <v>135</v>
       </c>
       <c r="C68" t="n">
-        <v>0.602320700736056</v>
+        <v>0.269336616071375</v>
       </c>
       <c r="D68" t="n">
-        <v>0.611310561941071</v>
+        <v>0.285416414045785</v>
       </c>
       <c r="E68" t="n">
-        <v>1.16964285714286</v>
+        <v>3.72809430255403</v>
       </c>
       <c r="F68" t="n">
-        <v>0.592968283535925</v>
+        <v>4.89048920547602</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I68" t="n">
-        <v>0.213738100606262</v>
+        <v>0.54452105461125</v>
       </c>
       <c r="J68" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
@@ -3187,28 +3310,124 @@
         <v>137</v>
       </c>
       <c r="C69" t="n">
-        <v>0.627314398715263</v>
+        <v>0.298186794099356</v>
       </c>
       <c r="D69" t="n">
-        <v>0.627314398715263</v>
+        <v>0.311342093839034</v>
       </c>
       <c r="E69" t="n">
-        <v>1.08817733990148</v>
+        <v>3.29240174672489</v>
       </c>
       <c r="F69" t="n">
-        <v>0.507425179479766</v>
+        <v>3.98392188430328</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I69" t="n">
-        <v>0.202514744009264</v>
+        <v>0.506762158192706</v>
       </c>
       <c r="J69" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" t="s">
+        <v>139</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.332748090762633</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.342392962958651</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.8689178818112</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3.15686990578299</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.465475169753157</v>
+      </c>
+      <c r="J70" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.499198521700123</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.506329929152982</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.63768382352941</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.137783167262</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.295566400715425</v>
+      </c>
+      <c r="J71" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" t="s">
+        <v>143</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.522993828733475</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.522993828733475</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.52362068965517</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.987589013341955</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.28150343572701</v>
+      </c>
+      <c r="J72" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3230,7 +3449,7 @@
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="60.71" hidden="0" customWidth="1"/>
   </cols>
@@ -3269,322 +3488,386 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0000690248633798375</v>
+        <v>0.0000370514344902947</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000690248633798376</v>
+        <v>0.000444617213883536</v>
       </c>
       <c r="E2" t="n">
-        <v>221.8</v>
+        <v>332.733333333333</v>
       </c>
       <c r="F2" t="n">
-        <v>2125.07551027874</v>
+        <v>3394.94590766807</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.25</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1609944442822</v>
+        <v>3.35201372708482</v>
       </c>
       <c r="J2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0014992198216207</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.00599687928648278</v>
+      </c>
+      <c r="E3" t="n">
+        <v>999.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6499.55901988972</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.22207469315689</v>
+      </c>
+      <c r="J3" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.00479070309341298</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0239535154670649</v>
-      </c>
-      <c r="E3" t="n">
-        <v>259.493506493507</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1385.97508325908</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.62063073962279</v>
-      </c>
-      <c r="J3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0166797975569069</v>
+        <v>0.0014992198216207</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0396583229023702</v>
+        <v>0.00599687928648278</v>
       </c>
       <c r="E4" t="n">
-        <v>69.5156794425087</v>
+        <v>999.5</v>
       </c>
       <c r="F4" t="n">
-        <v>284.566397512524</v>
+        <v>6499.55901988972</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I4" t="n">
-        <v>1.40166565547733</v>
+        <v>2.22207469315689</v>
       </c>
       <c r="J4" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0198291614511851</v>
+        <v>0.00329582567641046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0396583229023702</v>
+        <v>0.00988747702923139</v>
       </c>
       <c r="E5" t="n">
-        <v>58.1428571428571</v>
+        <v>399.68</v>
       </c>
       <c r="F5" t="n">
-        <v>227.954980151296</v>
+        <v>2284.21059157039</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I5" t="n">
-        <v>1.40166565547733</v>
+        <v>2.00491451245403</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C6" t="n">
-        <v>0.013877379587164</v>
+        <v>0.00766814018589269</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0396583229023702</v>
+        <v>0.0184035364461425</v>
       </c>
       <c r="E6" t="n">
-        <v>13.9978494623656</v>
+        <v>20.9989247311828</v>
       </c>
       <c r="F6" t="n">
-        <v>59.8757329376123</v>
+        <v>102.279067321024</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.25</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>1.40166565547733</v>
+        <v>1.7350987144106</v>
       </c>
       <c r="J6" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0280542928380034</v>
+        <v>0.0149082847993736</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0467571547300056</v>
+        <v>0.0298165695987473</v>
       </c>
       <c r="E7" t="n">
-        <v>40.6571428571429</v>
+        <v>81.4081632653061</v>
       </c>
       <c r="F7" t="n">
-        <v>145.292919316992</v>
+        <v>342.389562344484</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I7" t="n">
-        <v>1.33015192442753</v>
+        <v>1.52554232366078</v>
       </c>
       <c r="J7" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0462444344043176</v>
+        <v>0.0348860358299779</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0526614728585067</v>
+        <v>0.0476794283634042</v>
       </c>
       <c r="E8" t="n">
-        <v>24.2673992673993</v>
+        <v>33.9777777777778</v>
       </c>
       <c r="F8" t="n">
-        <v>74.5934754816134</v>
+        <v>114.018163662715</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I8" t="n">
-        <v>1.27850699852701</v>
+        <v>1.32166896006537</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C9" t="n">
-        <v>0.047395325572656</v>
+        <v>0.0357595712725532</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0526614728585067</v>
+        <v>0.0476794283634042</v>
       </c>
       <c r="E9" t="n">
-        <v>23.6571428571429</v>
+        <v>33.1233333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>72.1361092632249</v>
+        <v>110.331747088977</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I9" t="n">
-        <v>1.27850699852701</v>
+        <v>1.32166896006537</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C10" t="n">
-        <v>0.047395325572656</v>
+        <v>0.0357595712725532</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0526614728585067</v>
+        <v>0.0476794283634042</v>
       </c>
       <c r="E10" t="n">
-        <v>23.6571428571429</v>
+        <v>33.1233333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>72.1361092632249</v>
+        <v>110.331747088977</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>1.27850699852701</v>
+        <v>1.32166896006537</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B11" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="C11" t="n">
-        <v>0.193707111727762</v>
+        <v>0.0585267307609904</v>
       </c>
       <c r="D11" t="n">
-        <v>0.193707111727762</v>
+        <v>0.0702320769131885</v>
       </c>
       <c r="E11" t="n">
-        <v>5.24582210242588</v>
+        <v>19.894472361809</v>
       </c>
       <c r="F11" t="n">
-        <v>8.61053433442562</v>
+        <v>56.4659177521415</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I11" t="n">
-        <v>0.712854434379359</v>
+        <v>1.15346448837426</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0670542795241716</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0731501231172781</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.2620087336245</v>
+      </c>
+      <c r="F12" t="n">
+        <v>46.6463122182289</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.13578493858707</v>
+      </c>
+      <c r="J12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.149110432986687</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.149110432986687</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7.34490566037736</v>
+      </c>
+      <c r="F13" t="n">
+        <v>13.9778555611783</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.826491968686295</v>
+      </c>
+      <c r="J13" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3606,7 +3889,7 @@
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="60.71" hidden="0" customWidth="1"/>
   </cols>
@@ -3645,386 +3928,482 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0253193180336771</v>
+        <v>0.00336051193499512</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0716630861195948</v>
+        <v>0.0504076790249268</v>
       </c>
       <c r="E2" t="n">
-        <v>45.1904761904762</v>
+        <v>32.3848684210526</v>
       </c>
       <c r="F2" t="n">
-        <v>166.12866893112</v>
+        <v>184.453262983703</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>1.14470449318566</v>
+        <v>1.29750329879023</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0264922734714403</v>
+        <v>0.0190492685407353</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0716630861195948</v>
+        <v>0.0563464267966121</v>
       </c>
       <c r="E3" t="n">
-        <v>43.1298701298701</v>
+        <v>63.2730158730159</v>
       </c>
       <c r="F3" t="n">
-        <v>156.600338426129</v>
+        <v>250.607115446019</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I3" t="n">
-        <v>1.14470449318566</v>
+        <v>1.24913361948864</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0307825507393775</v>
+        <v>0.0199347325407438</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0716630861195948</v>
+        <v>0.0563464267966121</v>
       </c>
       <c r="E4" t="n">
-        <v>36.948051948052</v>
+        <v>60.3878787878788</v>
       </c>
       <c r="F4" t="n">
-        <v>128.609048349639</v>
+        <v>236.436161492859</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I4" t="n">
-        <v>1.14470449318566</v>
+        <v>1.24913361948864</v>
       </c>
       <c r="J4" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00614717984176483</v>
+        <v>0.0267011909686245</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0716630861195948</v>
+        <v>0.0563464267966121</v>
       </c>
       <c r="E5" t="n">
-        <v>21.5877192982456</v>
+        <v>44.7303370786517</v>
       </c>
       <c r="F5" t="n">
-        <v>109.919525867581</v>
+        <v>162.060118437595</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.25</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I5" t="n">
-        <v>1.14470449318566</v>
+        <v>1.24913361948864</v>
       </c>
       <c r="J5" t="s">
-        <v>167</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0354439777386331</v>
+        <v>0.0269944994833615</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0716630861195948</v>
+        <v>0.0563464267966121</v>
       </c>
       <c r="E6" t="n">
-        <v>31.9470304975923</v>
+        <v>44.2311111111111</v>
       </c>
       <c r="F6" t="n">
-        <v>106.696753821913</v>
+        <v>159.76817645418</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I6" t="n">
-        <v>1.14470449318566</v>
+        <v>1.24913361948864</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0358315430597974</v>
+        <v>0.0171549810602662</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0716630861195948</v>
+        <v>0.0563464267966121</v>
       </c>
       <c r="E7" t="n">
-        <v>31.5904761904762</v>
+        <v>8.72470817120623</v>
       </c>
       <c r="F7" t="n">
-        <v>105.162379101859</v>
+        <v>35.4700105957832</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.14470449318566</v>
+        <v>1.24913361948864</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0526522433401142</v>
+        <v>0.0300514276248598</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0902609885830529</v>
+        <v>0.0563464267966121</v>
       </c>
       <c r="E8" t="n">
-        <v>6.65932144106331</v>
+        <v>9.9900314795383</v>
       </c>
       <c r="F8" t="n">
-        <v>19.6053515331692</v>
+        <v>35.0135129879438</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.25</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>1.04449991418155</v>
+        <v>1.24913361948864</v>
       </c>
       <c r="J8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C9" t="n">
-        <v>0.069408326255472</v>
+        <v>0.0176875187806402</v>
       </c>
       <c r="D9" t="n">
-        <v>0.104112489383208</v>
+        <v>0.0563464267966121</v>
       </c>
       <c r="E9" t="n">
-        <v>15.9020866773676</v>
+        <v>8.61712361712362</v>
       </c>
       <c r="F9" t="n">
-        <v>42.422766986769</v>
+        <v>34.7691979742289</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.982497169193983</v>
+        <v>1.24913361948864</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0906068463642597</v>
+        <v>0.052518881698076</v>
       </c>
       <c r="D10" t="n">
-        <v>0.12080912848568</v>
+        <v>0.0875314694967932</v>
       </c>
       <c r="E10" t="n">
-        <v>12.0103343465046</v>
+        <v>22.2651685393258</v>
       </c>
       <c r="F10" t="n">
-        <v>28.8395211186174</v>
+        <v>65.6061564818719</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.917900248652175</v>
+        <v>1.05783578044384</v>
       </c>
       <c r="J10" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C11" t="n">
-        <v>0.120361565278333</v>
+        <v>0.0596674758349562</v>
       </c>
       <c r="D11" t="n">
-        <v>0.144433878334</v>
+        <v>0.0895012137524342</v>
       </c>
       <c r="E11" t="n">
-        <v>8.86660657954033</v>
+        <v>19.4985221674877</v>
       </c>
       <c r="F11" t="n">
-        <v>18.7728673115885</v>
+        <v>54.9657139453661</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I11" t="n">
-        <v>0.840330926933831</v>
+        <v>1.04817107504822</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C12" t="n">
-        <v>0.195695105113042</v>
+        <v>0.0861453452027456</v>
       </c>
       <c r="D12" t="n">
-        <v>0.199156288826046</v>
+        <v>0.108460235238325</v>
       </c>
       <c r="E12" t="n">
-        <v>2.90633608815427</v>
+        <v>13.2639730639731</v>
       </c>
       <c r="F12" t="n">
-        <v>4.74080792019254</v>
+        <v>32.5195394025965</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.25</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I12" t="n">
-        <v>0.700805975173172</v>
+        <v>0.964729457962561</v>
       </c>
       <c r="J12" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B13" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C13" t="n">
-        <v>0.199156288826046</v>
+        <v>0.0916979944934551</v>
       </c>
       <c r="D13" t="n">
-        <v>0.199156288826046</v>
+        <v>0.108460235238325</v>
       </c>
       <c r="E13" t="n">
-        <v>2.87051282051282</v>
+        <v>12.4145110410095</v>
       </c>
       <c r="F13" t="n">
-        <v>4.63204719436136</v>
+        <v>29.6614297251681</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.25</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I13" t="n">
-        <v>0.700805975173172</v>
+        <v>0.964729457962561</v>
       </c>
       <c r="J13" t="s">
-        <v>182</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.101347479208919</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.108460235238325</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11.1602272727273</v>
+      </c>
+      <c r="F14" t="n">
+        <v>25.5479953811899</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.964729457962561</v>
+      </c>
+      <c r="J14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.106276709803964</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.108460235238325</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.6075675675676</v>
+      </c>
+      <c r="F15" t="n">
+        <v>23.779080918829</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.964729457962561</v>
+      </c>
+      <c r="J15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.108460235238325</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.108460235238325</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.378835978836</v>
+      </c>
+      <c r="F16" t="n">
+        <v>23.0552521972299</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.964729457962561</v>
+      </c>
+      <c r="J16" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -4046,7 +4425,7 @@
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="60.71" hidden="0" customWidth="1"/>
   </cols>
@@ -4085,31 +4464,31 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0307825507393775</v>
+        <v>0.000283828364571552</v>
       </c>
       <c r="D2" t="n">
-        <v>0.106895406468325</v>
+        <v>0.00879867930171812</v>
       </c>
       <c r="E2" t="n">
-        <v>36.948051948052</v>
+        <v>115.744186046512</v>
       </c>
       <c r="F2" t="n">
-        <v>128.609048349639</v>
+        <v>945.29907031098</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.971040956983196</v>
+        <v>2.05558251137495</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -4117,31 +4496,31 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0346684381611494</v>
+        <v>0.000854709539721723</v>
       </c>
       <c r="D3" t="n">
-        <v>0.106895406468325</v>
+        <v>0.0118785571704819</v>
       </c>
       <c r="E3" t="n">
-        <v>32.6847290640394</v>
+        <v>65.705298013245</v>
       </c>
       <c r="F3" t="n">
-        <v>109.883626356627</v>
+        <v>464.191429653511</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>0.971040956983196</v>
+        <v>1.92523630775148</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -4149,31 +4528,31 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0362189721188044</v>
+        <v>0.0014392276912047</v>
       </c>
       <c r="D4" t="n">
-        <v>0.106895406468325</v>
+        <v>0.0118785571704819</v>
       </c>
       <c r="E4" t="n">
-        <v>31.2417582417582</v>
+        <v>50.246192893401</v>
       </c>
       <c r="F4" t="n">
-        <v>103.665533856838</v>
+        <v>328.793431531832</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.971040956983196</v>
+        <v>1.92523630775148</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
@@ -4181,31 +4560,31 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0393135041520565</v>
+        <v>0.00188315349863043</v>
       </c>
       <c r="D5" t="n">
-        <v>0.106895406468325</v>
+        <v>0.0118785571704819</v>
       </c>
       <c r="E5" t="n">
-        <v>28.7056277056277</v>
+        <v>43.7345132743363</v>
       </c>
       <c r="F5" t="n">
-        <v>92.8967850071638</v>
+        <v>274.425652536979</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I5" t="n">
-        <v>0.971040956983196</v>
+        <v>1.92523630775148</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -4213,31 +4592,31 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0393135041520565</v>
+        <v>0.00191589631781967</v>
       </c>
       <c r="D6" t="n">
-        <v>0.106895406468325</v>
+        <v>0.0118785571704819</v>
       </c>
       <c r="E6" t="n">
-        <v>28.7056277056277</v>
+        <v>43.3464912280702</v>
       </c>
       <c r="F6" t="n">
-        <v>92.8967850071638</v>
+        <v>271.243690750337</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.971040956983196</v>
+        <v>1.92523630775148</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
@@ -4245,63 +4624,63 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0400857774256217</v>
+        <v>0.0038505575448098</v>
       </c>
       <c r="D7" t="n">
-        <v>0.106895406468325</v>
+        <v>0.0198945473148506</v>
       </c>
       <c r="E7" t="n">
-        <v>28.1343705799151</v>
+        <v>30.1656441717791</v>
       </c>
       <c r="F7" t="n">
-        <v>90.5007775576607</v>
+        <v>167.707024685575</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I7" t="n">
-        <v>0.971040956983196</v>
+        <v>1.70126593844266</v>
       </c>
       <c r="J7" t="s">
-        <v>195</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0538941184428828</v>
+        <v>0.0044953059420577</v>
       </c>
       <c r="D8" t="n">
-        <v>0.108794467476642</v>
+        <v>0.0199077834576841</v>
       </c>
       <c r="E8" t="n">
-        <v>20.70385818561</v>
+        <v>27.8201133144476</v>
       </c>
       <c r="F8" t="n">
-        <v>60.4704610187662</v>
+        <v>150.359965971438</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.125</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>0.963393189246826</v>
+        <v>1.70097709184023</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
@@ -4309,290 +4688,770 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0595960981777748</v>
+        <v>0.0231757383378881</v>
       </c>
       <c r="D9" t="n">
-        <v>0.108794467476642</v>
+        <v>0.0591101427146882</v>
       </c>
       <c r="E9" t="n">
-        <v>18.6466165413534</v>
+        <v>51.7324675324675</v>
       </c>
       <c r="F9" t="n">
-        <v>52.5865385804282</v>
+        <v>194.754598138502</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I9" t="n">
-        <v>0.963393189246826</v>
+        <v>1.22833799209542</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0761488191827759</v>
+        <v>0.02523354305099</v>
       </c>
       <c r="D10" t="n">
-        <v>0.108794467476642</v>
+        <v>0.0591101427146882</v>
       </c>
       <c r="E10" t="n">
-        <v>14.4285714285714</v>
+        <v>47.4047619047619</v>
       </c>
       <c r="F10" t="n">
-        <v>37.1545194755331</v>
+        <v>174.429665770154</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.963393189246826</v>
+        <v>1.22833799209542</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="B11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C11" t="n">
-        <v>0.076895119183702</v>
+        <v>0.025527220063161</v>
       </c>
       <c r="D11" t="n">
-        <v>0.108794467476642</v>
+        <v>0.0591101427146882</v>
       </c>
       <c r="E11" t="n">
-        <v>14.2813852813853</v>
+        <v>46.8447058823529</v>
       </c>
       <c r="F11" t="n">
-        <v>36.6362215228568</v>
+        <v>171.826846938568</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I11" t="n">
-        <v>0.963393189246826</v>
+        <v>1.22833799209542</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0809903476493452</v>
+        <v>0.0272877343434333</v>
       </c>
       <c r="D12" t="n">
-        <v>0.108794467476642</v>
+        <v>0.0591101427146882</v>
       </c>
       <c r="E12" t="n">
-        <v>13.5222146274778</v>
+        <v>43.7428571428571</v>
       </c>
       <c r="F12" t="n">
-        <v>33.9870763057985</v>
+        <v>157.531937452816</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I12" t="n">
-        <v>0.963393189246826</v>
+        <v>1.22833799209542</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B13" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0876573461487165</v>
+        <v>0.0290455975649231</v>
       </c>
       <c r="D13" t="n">
-        <v>0.108794467476642</v>
+        <v>0.0591101427146882</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4386406544997</v>
+        <v>41.0247422680412</v>
       </c>
       <c r="F13" t="n">
-        <v>30.2796299619726</v>
+        <v>145.181982637693</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I13" t="n">
-        <v>0.963393189246826</v>
+        <v>1.22833799209542</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0883955048247714</v>
+        <v>0.0296309633944118</v>
       </c>
       <c r="D14" t="n">
-        <v>0.108794467476642</v>
+        <v>0.0591101427146882</v>
       </c>
       <c r="E14" t="n">
-        <v>12.3287585776669</v>
+        <v>40.1919191919192</v>
       </c>
       <c r="F14" t="n">
-        <v>29.9087565966534</v>
+        <v>141.432767389918</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I14" t="n">
-        <v>0.963393189246826</v>
+        <v>1.22833799209542</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B15" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C15" t="n">
-        <v>0.123931244775128</v>
+        <v>0.0296309633944118</v>
       </c>
       <c r="D15" t="n">
-        <v>0.141635708314432</v>
+        <v>0.0591101427146882</v>
       </c>
       <c r="E15" t="n">
-        <v>8.5910878112713</v>
+        <v>40.1919191919192</v>
       </c>
       <c r="F15" t="n">
-        <v>17.9384348623992</v>
+        <v>141.432767389918</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I15" t="n">
-        <v>0.84882724121637</v>
+        <v>1.22833799209542</v>
       </c>
       <c r="J15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B16" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C16" t="n">
-        <v>0.13350614314527</v>
+        <v>0.030216035137483</v>
       </c>
       <c r="D16" t="n">
-        <v>0.142406552688288</v>
+        <v>0.0591101427146882</v>
       </c>
       <c r="E16" t="n">
-        <v>7.92493946731235</v>
+        <v>39.3920792079208</v>
       </c>
       <c r="F16" t="n">
-        <v>15.9577198159978</v>
+        <v>137.847953827989</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I16" t="n">
-        <v>0.846470026633917</v>
+        <v>1.22833799209542</v>
       </c>
       <c r="J16" t="s">
-        <v>15</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C17" t="n">
-        <v>0.191716729420111</v>
+        <v>0.0305084607559681</v>
       </c>
       <c r="D17" t="n">
-        <v>0.191716729420111</v>
+        <v>0.0591101427146882</v>
       </c>
       <c r="E17" t="n">
-        <v>5.30752453653217</v>
+        <v>39.0039215686275</v>
       </c>
       <c r="F17" t="n">
-        <v>8.76663127972961</v>
+        <v>136.113983347048</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.125</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I17" t="n">
-        <v>0.717339988437364</v>
+        <v>1.22833799209542</v>
       </c>
       <c r="J17" t="s">
-        <v>15</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.040697170601244</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0742124875669744</v>
+      </c>
+      <c r="E18" t="n">
+        <v>28.9883211678832</v>
+      </c>
+      <c r="F18" t="n">
+        <v>92.8089136026139</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.12952301082445</v>
+      </c>
+      <c r="J18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0444587497780508</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0765678468399763</v>
+      </c>
+      <c r="E19" t="n">
+        <v>26.4586666666667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>82.3709488470273</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.11595356550453</v>
+      </c>
+      <c r="J19" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B20" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0556698218369758</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.085553985891766</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20.957671957672</v>
+      </c>
+      <c r="F20" t="n">
+        <v>60.5324018123073</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.06775975221903</v>
+      </c>
+      <c r="J20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0576704153745895</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.085553985891766</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20.2020408163265</v>
+      </c>
+      <c r="F21" t="n">
+        <v>57.6366440405093</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.06775975221903</v>
+      </c>
+      <c r="J21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>236</v>
+      </c>
+      <c r="B22" t="s">
+        <v>237</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0579559259266802</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.085553985891766</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20.0984771573604</v>
+      </c>
+      <c r="F22" t="n">
+        <v>57.2419191817422</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.06775975221903</v>
+      </c>
+      <c r="J22" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>238</v>
+      </c>
+      <c r="B23" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0613764336739604</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0864849747223987</v>
+      </c>
+      <c r="E23" t="n">
+        <v>18.933014354067</v>
+      </c>
+      <c r="F23" t="n">
+        <v>52.836918536863</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.06305933718208</v>
+      </c>
+      <c r="J23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>240</v>
+      </c>
+      <c r="B24" t="s">
+        <v>241</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.071011717989692</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0957114459861066</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.2559670781893</v>
+      </c>
+      <c r="F24" t="n">
+        <v>42.9955759555716</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.01903612250151</v>
+      </c>
+      <c r="J24" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>242</v>
+      </c>
+      <c r="B25" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0763601439895147</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0964265559742815</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.0625954198473</v>
+      </c>
+      <c r="F25" t="n">
+        <v>38.7454297644861</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.0158033444703</v>
+      </c>
+      <c r="J25" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>244</v>
+      </c>
+      <c r="B26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0777633515921625</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0964265559742815</v>
+      </c>
+      <c r="E26" t="n">
+        <v>14.7767790262172</v>
+      </c>
+      <c r="F26" t="n">
+        <v>37.7411499252725</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.0158033444703</v>
+      </c>
+      <c r="J26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>246</v>
+      </c>
+      <c r="B27" t="s">
+        <v>247</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0850314280432312</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.100504471083851</v>
+      </c>
+      <c r="E27" t="n">
+        <v>13.4477815699659</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33.1452091552853</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.997814617608139</v>
+      </c>
+      <c r="J27" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0875361522343221</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.100504471083851</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13.041059602649</v>
+      </c>
+      <c r="F28" t="n">
+        <v>31.7641532471192</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.997814617608139</v>
+      </c>
+      <c r="J28" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>250</v>
+      </c>
+      <c r="B29" t="s">
+        <v>251</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.103814918648103</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.114937945646114</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10.8770083102493</v>
+      </c>
+      <c r="F29" t="n">
+        <v>24.6380074459929</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.939536569535102</v>
+      </c>
+      <c r="J29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>252</v>
+      </c>
+      <c r="B30" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.108460235238325</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.115940251461658</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10.378835978836</v>
+      </c>
+      <c r="F30" t="n">
+        <v>23.0552521972299</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.935765762027245</v>
+      </c>
+      <c r="J30" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>253</v>
+      </c>
+      <c r="B31" t="s">
+        <v>254</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.132720144342348</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.13714414915376</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8.34444444444444</v>
+      </c>
+      <c r="F31" t="n">
+        <v>16.8517102410345</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.862822715543504</v>
+      </c>
+      <c r="J31" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>255</v>
+      </c>
+      <c r="B32" t="s">
+        <v>256</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.147535645706635</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.147535645706635</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7.43129770992366</v>
+      </c>
+      <c r="F32" t="n">
+        <v>14.2211664253922</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.831103038238941</v>
+      </c>
+      <c r="J32" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Paired_sample_test/Results/GeneOntology/GeneOntology_down_regulated.xlsx
+++ b/Paired_sample_test/Results/GeneOntology/GeneOntology_down_regulated.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
   <si>
     <t xml:space="preserve">Term</t>
   </si>
@@ -56,262 +56,250 @@
     <t xml:space="preserve">FN1;SKAP1</t>
   </si>
   <si>
+    <t xml:space="preserve">Neural Crest Cell Migration Involved in Autonomic Nervous System Development (GO:1901166)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Cell-Cell Adhesion Mediated by Integrin (GO:0033634)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrin Activation (GO:0033622)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Adaptive Immune Response (GO:0002821)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enteric Nervous System Development (GO:0048484)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Integrin Activation (GO:0033625)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative Regulation of Transforming Growth Factor Beta Production (GO:0071635)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Cell-Cell Adhesion Mediated by Integrin (GO:0033632)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Leukocyte Cell-Cell Adhesion (GO:1903037)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Heterotypic Cell-Cell Adhesion (GO:0034116)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Integrin Activation (GO:0033623)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Transforming Growth Factor Beta Production (GO:0071634)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Adaptive Immune Response (GO:0002819)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autonomic Nervous System Development (GO:0048483)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Cell Adhesion Mediated by Integrin (GO:0033630)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Heterotypic Cell-Cell Adhesion (GO:0034114)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative Regulation of Leukocyte Activation (GO:0002695)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Protein Modification Process (GO:0031399)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Lymphocyte Activation (GO:0051249)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood Coagulation, Fibrin Clot Formation (GO:0072378)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein Activation Cascade (GO:0072376)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Fibroblast Proliferation (GO:0048146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell-substrate Junction Assembly (GO:0007044)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endodermal Cell Differentiation (GO:0035987)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesenchymal Cell Migration (GO:0090497)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endoderm Formation (GO:0001706)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neural Crest Cell Migration (GO:0001755)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Phosphorylation (GO:0042325)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substrate Adhesion-Dependent Cell Spreading (GO:0034446)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Fibroblast Proliferation (GO:0048145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endothelial Cell Migration (GO:0043542)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neural Crest Cell Development (GO:0014032)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Cell-Matrix Adhesion (GO:0001954)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nervous System Development (GO:0007399)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAMDC4;FN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Cell-Cell Adhesion (GO:0022409)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Leukocyte Cell-Cell Adhesion (GO:1903039)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Cell-Matrix Adhesion (GO:0001952)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of T Cell Activation (GO:0050863)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/83</t>
+  </si>
+  <si>
     <t xml:space="preserve">Integrin-mediated Signaling Pathway (GO:0007229)</t>
   </si>
   <si>
-    <t xml:space="preserve">2/87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGA11;FN1</t>
+    <t xml:space="preserve">1/87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T Cell Receptor Signaling Pathway (GO:0050852)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Protein Phosphorylation (GO:0001932)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Immune Response (GO:0050778)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Protein-Containing Complex Assembly (GO:0031334)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell Junction Assembly (GO:0034329)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/109</t>
   </si>
   <si>
     <t xml:space="preserve">Cell-matrix Adhesion (GO:0007160)</t>
   </si>
   <si>
-    <t xml:space="preserve">2/116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neural Crest Cell Migration Involved in Autonomic Nervous System Development (GO:1901166)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Cell-Cell Adhesion Mediated by Integrin (GO:0033634)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SKAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrin Activation (GO:0033622)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Adaptive Immune Response (GO:0002821)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collagen-activated Signaling Pathway (GO:0038065)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enteric Nervous System Development (GO:0048484)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Integrin Activation (GO:0033625)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative Regulation of Transforming Growth Factor Beta Production (GO:0071635)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Cell-Cell Adhesion Mediated by Integrin (GO:0033632)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Leukocyte Cell-Cell Adhesion (GO:1903037)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Heterotypic Cell-Cell Adhesion (GO:0034116)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substrate-dependent Cell Migration (GO:0006929)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Integrin Activation (GO:0033623)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Transforming Growth Factor Beta Production (GO:0071634)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Adaptive Immune Response (GO:0002819)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autonomic Nervous System Development (GO:0048483)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Cell Adhesion Mediated by Integrin (GO:0033630)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Heterotypic Cell-Cell Adhesion (GO:0034114)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative Regulation of Leukocyte Activation (GO:0002695)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Protein Modification Process (GO:0031399)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Lymphocyte Activation (GO:0051249)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blood Coagulation, Fibrin Clot Formation (GO:0072378)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protein Activation Cascade (GO:0072376)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Fibroblast Proliferation (GO:0048146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cell-substrate Junction Assembly (GO:0007044)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endodermal Cell Differentiation (GO:0035987)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesenchymal Cell Migration (GO:0090497)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endoderm Formation (GO:0001706)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neural Crest Cell Migration (GO:0001755)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Phosphorylation (GO:0042325)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substrate Adhesion-Dependent Cell Spreading (GO:0034446)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Fibroblast Proliferation (GO:0048145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endothelial Cell Migration (GO:0043542)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neural Crest Cell Development (GO:0014032)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Cell-Matrix Adhesion (GO:0001954)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Cell-Cell Adhesion (GO:0022409)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Leukocyte Cell-Cell Adhesion (GO:1903039)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muscle Organ Development (GO:0007517)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Cell-Matrix Adhesion (GO:0001952)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of T Cell Activation (GO:0050863)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T Cell Receptor Signaling Pathway (GO:0050852)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Protein Phosphorylation (GO:0001932)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Immune Response (GO:0050778)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Protein-Containing Complex Assembly (GO:0031334)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cell Junction Assembly (GO:0034329)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/109</t>
+    <t xml:space="preserve">1/116</t>
   </si>
   <si>
     <t xml:space="preserve">Antigen Receptor-Mediated Signaling Pathway (GO:0050851)</t>
@@ -389,397 +377,286 @@
     <t xml:space="preserve">1/486</t>
   </si>
   <si>
-    <t xml:space="preserve">Nervous System Development (GO:0007399)</t>
+    <t xml:space="preserve">Positive Regulation of RNA Biosynthetic Process (GO:1902680)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Cellular Process (GO:0048522)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Intracellular Signal Transduction (GO:1902533)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Cell Population Proliferation (GO:0042127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of Transcription by RNA Polymerase II (GO:0045944)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/1019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Gene Expression (GO:0010468)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/1146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive Regulation of DNA-templated Transcription (GO:0045893)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/1304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of DNA-templated Transcription (GO:0006355)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/2177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulation of Transcription by RNA Polymerase II (GO:0006357)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/2321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH2 Domain Binding (GO:0042169)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIT1;SKAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disulfide Oxidoreductase Activity (GO:0015036)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXNL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-stranded RNA Binding (GO:0003727)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZFR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3 Domain Binding (GO:0017124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinase Binding (GO:0019900)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double-stranded RNA Binding (GO:0003725)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phosphatase Binding (GO:0019902)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protease Binding (GO:0002020)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein Phosphatase Binding (GO:0019903)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein Kinase Binding (GO:0019901)</t>
   </si>
   <si>
     <t xml:space="preserve">1/531</t>
   </si>
   <si>
-    <t xml:space="preserve">Positive Regulation of RNA Biosynthetic Process (GO:1902680)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Cellular Process (GO:0048522)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Intracellular Signal Transduction (GO:1902533)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Cell Population Proliferation (GO:0042127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of Transcription by RNA Polymerase II (GO:0045944)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/1019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Gene Expression (GO:0010468)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/1146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Regulation of DNA-templated Transcription (GO:0045893)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/1304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of DNA-templated Transcription (GO:0006355)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/2177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulation of Transcription by RNA Polymerase II (GO:0006357)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/2321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH2 Domain Binding (GO:0042169)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIT1;SKAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collagen Receptor Activity (GO:0038064)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collagen Binding Involved in Cell-Matrix Adhesion (GO:0098639)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cell-matrix Adhesion Mediator Activity (GO:0098634)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinase Binding (GO:0019900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3 Domain Binding (GO:0017124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phosphatase Binding (GO:0019902)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protease Binding (GO:0002020)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protein Phosphatase Binding (GO:0019903)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GTP Binding (GO:0005525)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBB8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guanyl Ribonucleotide Binding (GO:0032561)</t>
+    <t xml:space="preserve">Supramolecular Fiber (GO:0099512)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platelet Alpha Granule Lumen (GO:0031093)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acrosomal Vesicle (GO:0001669)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACRV1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endoplasmic Reticulum Lumen (GO:0005788)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL26A1;FN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plasma Membrane Raft (GO:0044853)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platelet Alpha Granule (GO:0031091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intracellular Organelle Lumen (GO:0070013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membrane Raft (GO:0045121)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vesicle (GO:0031982)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretory Granule Lumen (GO:0034774)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extracellular Exosome (GO:0070062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/2059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIT1;FN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extracellular Vesicle (GO:1903561)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/2082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BACTERIAL INVASION OF EPITHELIAL CELLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECM-RECEPTOR INTERACTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMALL CELL LUNG CANCER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGE-RAGE SIGNALING PATHWAY IN DIABETIC COMPLICATIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMOEBIASIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROTEIN DIGESTION AND ABSORPTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL26A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YERSINIA INFECTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTEGRIN SIGNALING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROTEOGLYCANS IN CANCER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOCAL ADHESION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAP1 SIGNALING PATHWAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGULATION OF ACTIN CYTOSKELETON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYTOSKELETON IN MUSCLE CELLS</t>
   </si>
   <si>
     <t xml:space="preserve">1/230</t>
   </si>
   <si>
-    <t xml:space="preserve">Protein Kinase Binding (GO:0019901)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endoplasmic Reticulum Lumen (GO:0005788)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL26A1;FN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supramolecular Fiber (GO:0099512)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platelet Alpha Granule Lumen (GO:0031093)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plasma Membrane Raft (GO:0044853)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platelet Alpha Granule (GO:0031091)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extracellular Exosome (GO:0070062)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/2059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIT1;FN1;TUBB8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intracellular Organelle Lumen (GO:0070013)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extracellular Vesicle (GO:1903561)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/2082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Membrane Raft (GO:0045121)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microtubule (GO:0005874)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polymeric Cytoskeletal Fiber (GO:0099513)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretory Granule Lumen (GO:0034774)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microtubule Cytoskeleton (GO:0015630)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focal Adhesion (GO:0005925)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cell-substrate Junction (GO:0030055)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECM-RECEPTOR INTERACTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTEGRIN SIGNALING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOCAL ADHESION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGULATION OF ACTIN CYTOSKELETON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYTOSKELETON IN MUSCLE CELLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/230</t>
-  </si>
-  <si>
     <t xml:space="preserve">HUMAN PAPILLOMAVIRUS INFECTION</t>
   </si>
   <si>
-    <t xml:space="preserve">2/328</t>
+    <t xml:space="preserve">1/328</t>
   </si>
   <si>
     <t xml:space="preserve">PI3K-AKT SIGNALING PATHWAY</t>
   </si>
   <si>
-    <t xml:space="preserve">2/355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACTERIAL INVASION OF EPITHELIAL CELLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAP JUNCTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARRHYTHMOGENIC RIGHT VENTRICULAR CARDIOMYOPATHY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMALL CELL LUNG CANCER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYPERTROPHIC CARDIOMYOPATHY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGE-RAGE SIGNALING PATHWAY IN DIABETIC COMPLICATIONS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMOEBIASIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROTEIN DIGESTION AND ABSORPTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL26A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DILATED CARDIOMYOPATHY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YERSINIA INFECTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHAGOSOME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOTOR PROTEINS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROTEOGLYCANS IN CANCER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATHOGENIC ESCHERICHIA COLI INFECTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAP1 SIGNALING PATHWAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SALMONELLA INFECTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARKINSON DISEASE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRION DISEASE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IGSF CAM SIGNALING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUNTINGTON DISEASE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMYOTROPHIC LATERAL SCLEROSIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALZHEIMER DISEASE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATHWAYS OF NEURODEGENERATION - MULTIPLE DISEASES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/469</t>
+    <t xml:space="preserve">1/355</t>
   </si>
   <si>
     <t xml:space="preserve">PATHWAYS IN CANCER</t>
@@ -1121,7 +998,7 @@
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="60.71" hidden="0" customWidth="1"/>
   </cols>
@@ -1166,25 +1043,25 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000189920342634409</v>
+        <v>0.00035286890580878</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00984822287821286</v>
+        <v>0.023995085594997</v>
       </c>
       <c r="E2" t="n">
-        <v>142.314285714286</v>
+        <v>94.8666666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>1219.47771155407</v>
+        <v>754.13440259815</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="I2" t="n">
-        <v>2.00664213131124</v>
+        <v>1.61987769651845</v>
       </c>
       <c r="J2" t="s">
         <v>12</v>
@@ -1198,25 +1075,25 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000277414728963742</v>
+        <v>0.00199856343165899</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00984822287821286</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E3" t="n">
-        <v>117.111764705882</v>
+        <v>713.857142857143</v>
       </c>
       <c r="F3" t="n">
-        <v>959.144996337308</v>
+        <v>4436.8553176414</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I3" t="n">
-        <v>2.00664213131124</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -1230,60 +1107,60 @@
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000492704444715923</v>
+        <v>0.00279701502710506</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0116606718582768</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E4" t="n">
-        <v>87.1929824561404</v>
+        <v>475.857142857143</v>
       </c>
       <c r="F4" t="n">
-        <v>664.026970255321</v>
+        <v>2797.66050021554</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I4" t="n">
-        <v>1.93327642591181</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0014992198216207</v>
+        <v>0.00359490866621763</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0195003019187619</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E5" t="n">
-        <v>999.5</v>
+        <v>356.857142857143</v>
       </c>
       <c r="F5" t="n">
-        <v>6499.55901988972</v>
+        <v>2008.47646591344</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I5" t="n">
-        <v>1.70995866450224</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -1291,511 +1168,511 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00209838728197325</v>
+        <v>0.00359490866621763</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0195003019187619</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E6" t="n">
-        <v>666.266666666667</v>
+        <v>356.857142857143</v>
       </c>
       <c r="F6" t="n">
-        <v>4108.59082569121</v>
+        <v>2008.47646591344</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I6" t="n">
-        <v>1.70995866450224</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00269725593591418</v>
+        <v>0.00359490866621763</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0195003019187619</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E7" t="n">
-        <v>499.65</v>
+        <v>356.857142857143</v>
       </c>
       <c r="F7" t="n">
-        <v>2955.68973928353</v>
+        <v>2008.47646591344</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I7" t="n">
-        <v>1.70995866450224</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00269725593591418</v>
+        <v>0.00439224439616303</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0195003019187619</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E8" t="n">
-        <v>499.65</v>
+        <v>285.457142857143</v>
       </c>
       <c r="F8" t="n">
-        <v>2955.68973928353</v>
+        <v>1549.43708775113</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I8" t="n">
-        <v>1.70995866450224</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00269725593591418</v>
+        <v>0.00439224439616303</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0195003019187619</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E9" t="n">
-        <v>499.65</v>
+        <v>285.457142857143</v>
       </c>
       <c r="F9" t="n">
-        <v>2955.68973928353</v>
+        <v>1549.43708775113</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I9" t="n">
-        <v>1.70995866450224</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J9" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00269725593591418</v>
+        <v>0.00439224439616303</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0195003019187619</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E10" t="n">
-        <v>499.65</v>
+        <v>285.457142857143</v>
       </c>
       <c r="F10" t="n">
-        <v>2955.68973928353</v>
+        <v>1549.43708775113</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I10" t="n">
-        <v>1.70995866450224</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00329582567641046</v>
+        <v>0.00479070309341298</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0195003019187619</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E11" t="n">
-        <v>399.68</v>
+        <v>259.493506493507</v>
       </c>
       <c r="F11" t="n">
-        <v>2284.21059157039</v>
+        <v>1385.97508325908</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>1.70995866450224</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00329582567641046</v>
+        <v>0.00518902237949986</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0195003019187619</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E12" t="n">
-        <v>399.68</v>
+        <v>237.857142857143</v>
       </c>
       <c r="F12" t="n">
-        <v>2284.21059157039</v>
+        <v>1251.41637042065</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I12" t="n">
-        <v>1.70995866450224</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00329582567641046</v>
+        <v>0.00598524283644591</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0195003019187619</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E13" t="n">
-        <v>399.68</v>
+        <v>203.857142857143</v>
       </c>
       <c r="F13" t="n">
-        <v>2284.21059157039</v>
+        <v>1043.43429845216</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I13" t="n">
-        <v>1.70995866450224</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
         <v>34</v>
       </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
       <c r="C14" t="n">
-        <v>0.00359499844647963</v>
+        <v>0.00678090602009761</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0196342222846195</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E14" t="n">
-        <v>363.327272727273</v>
+        <v>178.357142857143</v>
       </c>
       <c r="F14" t="n">
-        <v>2044.88281453851</v>
+        <v>890.652175215938</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I14" t="n">
-        <v>1.70698629654215</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
         <v>36</v>
       </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
       <c r="C15" t="n">
-        <v>0.00389409648539669</v>
+        <v>0.0071785287204102</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0197486321759404</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E15" t="n">
-        <v>333.033333333333</v>
+        <v>167.857142857143</v>
       </c>
       <c r="F15" t="n">
-        <v>1847.7667100463</v>
+        <v>828.65378226444</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I15" t="n">
-        <v>1.70446297897488</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J15" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00419311979869468</v>
+        <v>0.0071785287204102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0198474337138215</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E16" t="n">
-        <v>307.4</v>
+        <v>167.857142857143</v>
       </c>
       <c r="F16" t="n">
-        <v>1682.80296780194</v>
+        <v>828.65378226444</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I16" t="n">
-        <v>1.70229563983173</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J16" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00449206839321453</v>
+        <v>0.00757601220630419</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0199335534948895</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E17" t="n">
-        <v>285.428571428571</v>
+        <v>158.52380952381</v>
       </c>
       <c r="F17" t="n">
-        <v>1542.86759275583</v>
+        <v>774.03503382755</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I17" t="n">
-        <v>1.70041527402117</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00508974145357057</v>
+        <v>0.00837056168160556</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0201358464035876</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E18" t="n">
-        <v>249.725</v>
+        <v>142.657142857143</v>
       </c>
       <c r="F18" t="n">
-        <v>1318.67991590424</v>
+        <v>682.334006028863</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I18" t="n">
-        <v>1.69603011024916</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C19" t="n">
-        <v>0.00538846593898824</v>
+        <v>0.0087676277457428</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0201358464035876</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E19" t="n">
-        <v>235.023529411765</v>
+        <v>135.857142857143</v>
       </c>
       <c r="F19" t="n">
-        <v>1227.6441242999</v>
+        <v>643.513034914984</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I19" t="n">
-        <v>1.69603011024916</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
         <v>45</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00538846593898824</v>
+        <v>0.00956134271782716</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0201358464035876</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E20" t="n">
-        <v>235.023529411765</v>
+        <v>124.031055900621</v>
       </c>
       <c r="F20" t="n">
-        <v>1227.6441242999</v>
+        <v>576.747772435402</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I20" t="n">
-        <v>1.69603011024916</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
         <v>47</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="n">
+        <v>0.0099579917015561</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.030779247077537</v>
+      </c>
+      <c r="E21" t="n">
+        <v>118.857142857143</v>
+      </c>
+      <c r="F21" t="n">
+        <v>547.857720990995</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.51174200809357</v>
+      </c>
+      <c r="J21" t="s">
         <v>48</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.00568711573898333</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.0201892608733908</v>
-      </c>
-      <c r="E21" t="n">
-        <v>221.955555555556</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1147.41079930952</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.69487958023831</v>
-      </c>
-      <c r="J21" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1803,639 +1680,639 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00628419133253944</v>
+        <v>0.0099579917015561</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0204191816738413</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E22" t="n">
-        <v>199.74</v>
+        <v>118.857142857143</v>
       </c>
       <c r="F22" t="n">
-        <v>1012.62549558717</v>
+        <v>547.857720990995</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I22" t="n">
-        <v>1.68996166683562</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00658261714792867</v>
+        <v>0.0099579917015561</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0204191816738413</v>
+        <v>0.030779247077537</v>
       </c>
       <c r="E23" t="n">
-        <v>190.219047619048</v>
+        <v>118.857142857143</v>
       </c>
       <c r="F23" t="n">
-        <v>955.531692191046</v>
+        <v>547.857720990995</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I23" t="n">
-        <v>1.68996166683562</v>
+        <v>1.51174200809357</v>
       </c>
       <c r="J23" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0071792448741713</v>
+        <v>0.0115431985365685</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0204191816738413</v>
+        <v>0.0341277174124634</v>
       </c>
       <c r="E24" t="n">
-        <v>173.660869565217</v>
+        <v>101.857142857143</v>
       </c>
       <c r="F24" t="n">
-        <v>857.287488456765</v>
+        <v>454.451826608544</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I24" t="n">
-        <v>1.68996166683562</v>
+        <v>1.46689275796579</v>
       </c>
       <c r="J24" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00747744681013907</v>
+        <v>0.0123349690429112</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0204191816738413</v>
+        <v>0.0349490789549149</v>
       </c>
       <c r="E25" t="n">
-        <v>166.416666666667</v>
+        <v>95.0571428571429</v>
       </c>
       <c r="F25" t="n">
-        <v>814.753347497614</v>
+        <v>417.80627965005</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I25" t="n">
-        <v>1.68996166683562</v>
+        <v>1.45656426512771</v>
       </c>
       <c r="J25" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
         <v>56</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00747744681013907</v>
+        <v>0.0131261847028175</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0204191816738413</v>
+        <v>0.0353641442470695</v>
       </c>
       <c r="E26" t="n">
-        <v>166.416666666667</v>
+        <v>89.1071428571429</v>
       </c>
       <c r="F26" t="n">
-        <v>814.753347497614</v>
+        <v>386.114278489562</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I26" t="n">
-        <v>1.68996166683562</v>
+        <v>1.45143684665186</v>
       </c>
       <c r="J26" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00747744681013907</v>
+        <v>0.013521584565056</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0204191816738413</v>
+        <v>0.0353641442470695</v>
       </c>
       <c r="E27" t="n">
-        <v>166.416666666667</v>
+        <v>86.4025974025974</v>
       </c>
       <c r="F27" t="n">
-        <v>814.753347497614</v>
+        <v>371.830814220732</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I27" t="n">
-        <v>1.68996166683562</v>
+        <v>1.45143684665186</v>
       </c>
       <c r="J27" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" t="s">
         <v>60</v>
       </c>
-      <c r="B28" t="s">
-        <v>61</v>
-      </c>
       <c r="C28" t="n">
-        <v>0.00866950866872135</v>
+        <v>0.0147069527624561</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0227975968696006</v>
+        <v>0.0357168852802504</v>
       </c>
       <c r="E28" t="n">
-        <v>142.614285714286</v>
+        <v>79.1904761904762</v>
       </c>
       <c r="F28" t="n">
-        <v>677.124522385392</v>
+        <v>334.139060567782</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I28" t="n">
-        <v>1.64211093024854</v>
+        <v>1.44712642113232</v>
       </c>
       <c r="J28" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00926509224971447</v>
+        <v>0.0147069527624561</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0234936267760617</v>
+        <v>0.0357168852802504</v>
       </c>
       <c r="E29" t="n">
-        <v>133.093333333333</v>
+        <v>79.1904761904762</v>
       </c>
       <c r="F29" t="n">
-        <v>623.076634648791</v>
+        <v>334.139060567782</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I29" t="n">
-        <v>1.62904993480822</v>
+        <v>1.44712642113232</v>
       </c>
       <c r="J29" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00986037774269364</v>
+        <v>0.0166797975569069</v>
       </c>
       <c r="D30" t="n">
-        <v>0.024040384019274</v>
+        <v>0.0369971465071827</v>
       </c>
       <c r="E30" t="n">
-        <v>124.7625</v>
+        <v>69.5156794425087</v>
       </c>
       <c r="F30" t="n">
-        <v>576.306782745311</v>
+        <v>284.566397512524</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I30" t="n">
-        <v>1.61905859922672</v>
+        <v>1.431831770635</v>
       </c>
       <c r="J30" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0101579087405383</v>
+        <v>0.0170739515504477</v>
       </c>
       <c r="D31" t="n">
-        <v>0.024040384019274</v>
+        <v>0.0369971465071827</v>
       </c>
       <c r="E31" t="n">
-        <v>120.975757575758</v>
+        <v>67.8571428571429</v>
       </c>
       <c r="F31" t="n">
-        <v>555.218564896445</v>
+        <v>276.192229579909</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I31" t="n">
-        <v>1.61905859922672</v>
+        <v>1.431831770635</v>
       </c>
       <c r="J31" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0110500548998868</v>
+        <v>0.01864918566892</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0245173093091238</v>
+        <v>0.0369971465071827</v>
       </c>
       <c r="E32" t="n">
-        <v>110.877777777778</v>
+        <v>61.944099378882</v>
       </c>
       <c r="F32" t="n">
-        <v>499.539856773497</v>
+        <v>246.658479823396</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I32" t="n">
-        <v>1.61052719387303</v>
+        <v>1.431831770635</v>
       </c>
       <c r="J32" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0110500548998868</v>
+        <v>0.01864918566892</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0245173093091238</v>
+        <v>0.0369971465071827</v>
       </c>
       <c r="E33" t="n">
-        <v>110.877777777778</v>
+        <v>61.944099378882</v>
       </c>
       <c r="F33" t="n">
-        <v>499.539856773497</v>
+        <v>246.658479823396</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I33" t="n">
-        <v>1.61052719387303</v>
+        <v>1.431831770635</v>
       </c>
       <c r="J33" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0125354765664382</v>
+        <v>0.01864918566892</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0267474349304824</v>
+        <v>0.0369971465071827</v>
       </c>
       <c r="E34" t="n">
-        <v>97.3317073170732</v>
+        <v>61.944099378882</v>
       </c>
       <c r="F34" t="n">
-        <v>426.234285540356</v>
+        <v>246.658479823396</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I34" t="n">
-        <v>1.57271786033252</v>
+        <v>1.431831770635</v>
       </c>
       <c r="J34" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0128323377374526</v>
+        <v>0.0190426489375205</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0267474349304824</v>
+        <v>0.0369971465071827</v>
       </c>
       <c r="E35" t="n">
-        <v>95.0095238095238</v>
+        <v>60.6231003039514</v>
       </c>
       <c r="F35" t="n">
-        <v>413.841239970083</v>
+        <v>240.132594562701</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I35" t="n">
-        <v>1.57271786033252</v>
+        <v>1.431831770635</v>
       </c>
       <c r="J35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0140190390147642</v>
+        <v>0.0177166935480221</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0267474349304824</v>
+        <v>0.0369971465071827</v>
       </c>
       <c r="E36" t="n">
-        <v>86.7304347826087</v>
+        <v>12.2640201638311</v>
       </c>
       <c r="F36" t="n">
-        <v>370.10816194385</v>
+        <v>49.4638341302194</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>0.166666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="I36" t="n">
-        <v>1.57271786033252</v>
+        <v>1.431831770635</v>
       </c>
       <c r="J36" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
         <v>76</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0140190390147642</v>
+        <v>0.0202222107748752</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0267474349304824</v>
+        <v>0.0371651441267977</v>
       </c>
       <c r="E37" t="n">
-        <v>86.7304347826087</v>
+        <v>56.9771428571429</v>
       </c>
       <c r="F37" t="n">
-        <v>370.10816194385</v>
+        <v>222.266337799251</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I37" t="n">
-        <v>1.57271786033252</v>
+        <v>1.42986417865946</v>
       </c>
       <c r="J37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
         <v>76</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0140190390147642</v>
+        <v>0.0202222107748752</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0267474349304824</v>
+        <v>0.0371651441267977</v>
       </c>
       <c r="E38" t="n">
-        <v>86.7304347826087</v>
+        <v>56.9771428571429</v>
       </c>
       <c r="F38" t="n">
-        <v>370.10816194385</v>
+        <v>222.266337799251</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I38" t="n">
-        <v>1.57271786033252</v>
+        <v>1.42986417865946</v>
       </c>
       <c r="J38" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" t="s">
         <v>79</v>
       </c>
-      <c r="B39" t="s">
-        <v>80</v>
-      </c>
       <c r="C39" t="n">
-        <v>0.0143155285543427</v>
+        <v>0.0268829840764005</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0267474349304824</v>
+        <v>0.0481063925577693</v>
       </c>
       <c r="E39" t="n">
-        <v>84.8808510638298</v>
+        <v>42.4840085287846</v>
       </c>
       <c r="F39" t="n">
-        <v>360.43893024633</v>
+        <v>153.63329523077</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I39" t="n">
-        <v>1.57271786033252</v>
+        <v>1.31779720911272</v>
       </c>
       <c r="J39" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" t="s">
         <v>81</v>
       </c>
-      <c r="B40" t="s">
-        <v>82</v>
-      </c>
       <c r="C40" t="n">
-        <v>0.0152045515346865</v>
+        <v>0.0327272017891214</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0269880789740686</v>
+        <v>0.0570628133759041</v>
       </c>
       <c r="E40" t="n">
-        <v>79.776</v>
+        <v>34.6864111498258</v>
       </c>
       <c r="F40" t="n">
-        <v>333.955136289159</v>
+        <v>118.611871734907</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I40" t="n">
-        <v>1.5688280276574</v>
+        <v>1.24364682006923</v>
       </c>
       <c r="J40" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" t="s">
         <v>83</v>
       </c>
-      <c r="B41" t="s">
-        <v>82</v>
-      </c>
       <c r="C41" t="n">
-        <v>0.0152045515346865</v>
+        <v>0.0342804638132286</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0269880789740686</v>
+        <v>0.0582767884824887</v>
       </c>
       <c r="E41" t="n">
-        <v>79.776</v>
+        <v>33.0664451827243</v>
       </c>
       <c r="F41" t="n">
-        <v>333.955136289159</v>
+        <v>111.539060160258</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I41" t="n">
-        <v>1.5688280276574</v>
+        <v>1.2345043893448</v>
       </c>
       <c r="J41" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -2446,28 +2323,28 @@
         <v>85</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0178676130920248</v>
+        <v>0.037380442146754</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0309414763300917</v>
+        <v>0.0619968308775432</v>
       </c>
       <c r="E42" t="n">
-        <v>67.5762711864407</v>
+        <v>30.2401215805471</v>
       </c>
       <c r="F42" t="n">
-        <v>271.978646877106</v>
+        <v>99.3874148810262</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I42" t="n">
-        <v>1.50945896837692</v>
+        <v>1.20763050997872</v>
       </c>
       <c r="J42" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
@@ -2478,28 +2355,28 @@
         <v>87</v>
       </c>
       <c r="C43" t="n">
-        <v>0.020229739174506</v>
+        <v>0.0396997087104848</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0341978924140459</v>
+        <v>0.0637394427890858</v>
       </c>
       <c r="E43" t="n">
-        <v>59.4835820895522</v>
+        <v>28.4171428571429</v>
       </c>
       <c r="F43" t="n">
-        <v>232.021750766537</v>
+        <v>91.6853944819699</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I43" t="n">
-        <v>1.4660006583051</v>
+        <v>1.19559173745286</v>
       </c>
       <c r="J43" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -2510,28 +2387,28 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0246459677840751</v>
+        <v>0.0412431688635261</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0406945049457984</v>
+        <v>0.0637394427890858</v>
       </c>
       <c r="E44" t="n">
-        <v>48.5658536585366</v>
+        <v>27.3186813186813</v>
       </c>
       <c r="F44" t="n">
-        <v>179.846251021588</v>
+        <v>87.099326165868</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I44" t="n">
-        <v>1.39046423040218</v>
+        <v>1.19559173745286</v>
       </c>
       <c r="J44" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -2539,127 +2416,127 @@
         <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0281669971363706</v>
+        <v>0.0412431688635261</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0454512908336889</v>
+        <v>0.0637394427890858</v>
       </c>
       <c r="E45" t="n">
-        <v>42.3404255319149</v>
+        <v>27.3186813186813</v>
       </c>
       <c r="F45" t="n">
-        <v>151.13856507235</v>
+        <v>87.099326165868</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I45" t="n">
-        <v>1.34245377814086</v>
+        <v>1.19559173745286</v>
       </c>
       <c r="J45" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" t="s">
         <v>92</v>
       </c>
-      <c r="B46" t="s">
-        <v>93</v>
-      </c>
       <c r="C46" t="n">
-        <v>0.0299235360194532</v>
+        <v>0.0427844580072879</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0469704149346112</v>
+        <v>0.0646520698776795</v>
       </c>
       <c r="E46" t="n">
-        <v>39.788</v>
+        <v>26.3015873015873</v>
       </c>
       <c r="F46" t="n">
-        <v>139.620466706137</v>
+        <v>82.8915663187741</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I46" t="n">
-        <v>1.32817560326116</v>
+        <v>1.1894175663433</v>
       </c>
       <c r="J46" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" t="s">
         <v>94</v>
       </c>
-      <c r="B47" t="s">
-        <v>95</v>
-      </c>
       <c r="C47" t="n">
-        <v>0.0310930915764328</v>
+        <v>0.0454764979116999</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0469704149346112</v>
+        <v>0.0672261273477303</v>
       </c>
       <c r="E47" t="n">
-        <v>38.25</v>
+        <v>24.6919254658385</v>
       </c>
       <c r="F47" t="n">
-        <v>132.756937975663</v>
+        <v>76.31186768318</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I47" t="n">
-        <v>1.32817560326116</v>
+        <v>1.17246190614753</v>
       </c>
       <c r="J47" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" t="s">
         <v>96</v>
       </c>
-      <c r="B48" t="s">
-        <v>95</v>
-      </c>
       <c r="C48" t="n">
-        <v>0.0310930915764328</v>
+        <v>0.0470118302742274</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0469704149346112</v>
+        <v>0.0680171161414354</v>
       </c>
       <c r="E48" t="n">
-        <v>38.25</v>
+        <v>23.8571428571429</v>
       </c>
       <c r="F48" t="n">
-        <v>132.756937975663</v>
+        <v>72.9397788805927</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I48" t="n">
-        <v>1.32817560326116</v>
+        <v>1.16738178567016</v>
       </c>
       <c r="J48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
@@ -2670,28 +2547,28 @@
         <v>98</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0322614719403215</v>
+        <v>0.0550369282195952</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0477200939117256</v>
+        <v>0.0779689816444265</v>
       </c>
       <c r="E49" t="n">
-        <v>36.8259259259259</v>
+        <v>20.2571428571429</v>
       </c>
       <c r="F49" t="n">
-        <v>126.455868700302</v>
+        <v>58.7406681681905</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I49" t="n">
-        <v>1.32129871032223</v>
+        <v>1.10807813807757</v>
       </c>
       <c r="J49" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -2702,28 +2579,28 @@
         <v>100</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0354684660279251</v>
+        <v>0.0671519530979639</v>
       </c>
       <c r="D50" t="n">
-        <v>0.051393083428218</v>
+        <v>0.0931904655237049</v>
       </c>
       <c r="E50" t="n">
-        <v>33.4033613445378</v>
+        <v>16.4617940199336</v>
       </c>
       <c r="F50" t="n">
-        <v>111.537539925918</v>
+        <v>44.4599683621174</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I50" t="n">
-        <v>1.28909532518916</v>
+        <v>1.03062851878615</v>
       </c>
       <c r="J50" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
@@ -2734,28 +2611,28 @@
         <v>102</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0415663206424517</v>
+        <v>0.0697839237890214</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0590241753122814</v>
+        <v>0.0949061363530691</v>
       </c>
       <c r="E51" t="n">
-        <v>28.3628571428571</v>
+        <v>15.8124501197127</v>
       </c>
       <c r="F51" t="n">
-        <v>90.2070755648637</v>
+        <v>42.0983020967207</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I51" t="n">
-        <v>1.22897007218363</v>
+        <v>1.02270570645448</v>
       </c>
       <c r="J51" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
@@ -2766,28 +2643,28 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0507964976461815</v>
+        <v>0.0772680713380292</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0707166928015468</v>
+        <v>0.103024095117372</v>
       </c>
       <c r="E52" t="n">
-        <v>23.0488372093023</v>
+        <v>14.2089016511127</v>
       </c>
       <c r="F52" t="n">
-        <v>68.6838723883163</v>
+        <v>36.3815297451556</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1504780581141</v>
+        <v>0.987061191287799</v>
       </c>
       <c r="J52" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -2798,28 +2675,28 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0528056923384244</v>
+        <v>0.0880264908328034</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0721000799236179</v>
+        <v>0.112939648615672</v>
       </c>
       <c r="E53" t="n">
-        <v>22.1396648044693</v>
+        <v>12.3834586466165</v>
       </c>
       <c r="F53" t="n">
-        <v>65.1157714862158</v>
+        <v>30.0932592904541</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I53" t="n">
-        <v>1.14206425386078</v>
+        <v>0.947153567798998</v>
       </c>
       <c r="J53" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -2827,95 +2704,95 @@
         <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0585267307609904</v>
+        <v>0.0880264908328034</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0784037336609494</v>
+        <v>0.112939648615672</v>
       </c>
       <c r="E54" t="n">
-        <v>19.894472361809</v>
+        <v>12.3834586466165</v>
       </c>
       <c r="F54" t="n">
-        <v>56.4659177521415</v>
+        <v>30.0932592904541</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I54" t="n">
-        <v>1.1056632553036</v>
+        <v>0.947153567798998</v>
       </c>
       <c r="J54" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" t="s">
         <v>109</v>
       </c>
-      <c r="B55" t="s">
-        <v>110</v>
-      </c>
       <c r="C55" t="n">
-        <v>0.0667710686239844</v>
+        <v>0.111020769576404</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0861953794964162</v>
+        <v>0.139803932059175</v>
       </c>
       <c r="E55" t="n">
-        <v>17.3385964912281</v>
+        <v>9.67157584683358</v>
       </c>
       <c r="F55" t="n">
-        <v>46.9266582025697</v>
+        <v>21.2584910558997</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I55" t="n">
-        <v>1.06451601390838</v>
+        <v>0.854480613657665</v>
       </c>
       <c r="J55" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" t="s">
         <v>111</v>
       </c>
-      <c r="B56" t="s">
-        <v>110</v>
-      </c>
       <c r="C56" t="n">
-        <v>0.0667710686239844</v>
+        <v>0.12784324623835</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0861953794964162</v>
+        <v>0.156741596889363</v>
       </c>
       <c r="E56" t="n">
-        <v>17.3385964912281</v>
+        <v>8.30684699915469</v>
       </c>
       <c r="F56" t="n">
-        <v>46.9266582025697</v>
+        <v>17.0867722934379</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I56" t="n">
-        <v>1.06451601390838</v>
+        <v>0.804815732936824</v>
       </c>
       <c r="J56" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -2926,28 +2803,28 @@
         <v>113</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0844740453220733</v>
+        <v>0.129616369895488</v>
       </c>
       <c r="D57" t="n">
-        <v>0.107101021747629</v>
+        <v>0.156741596889363</v>
       </c>
       <c r="E57" t="n">
-        <v>13.5415807560137</v>
+        <v>8.18367346938776</v>
       </c>
       <c r="F57" t="n">
-        <v>33.4654567722162</v>
+        <v>16.7206867967252</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I57" t="n">
-        <v>0.970206385963285</v>
+        <v>0.804815732936824</v>
       </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -2958,28 +2835,28 @@
         <v>115</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0974979888806524</v>
+        <v>0.131386338569025</v>
       </c>
       <c r="D58" t="n">
-        <v>0.120638655665644</v>
+        <v>0.156741596889363</v>
       </c>
       <c r="E58" t="n">
-        <v>11.6307692307692</v>
+        <v>8.064039408867</v>
       </c>
       <c r="F58" t="n">
-        <v>27.0755413416995</v>
+        <v>16.3668803990092</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I58" t="n">
-        <v>0.918513510998883</v>
+        <v>0.804815732936824</v>
       </c>
       <c r="J58" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -2990,28 +2867,28 @@
         <v>117</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0988743811445363</v>
+        <v>0.157560525915391</v>
       </c>
       <c r="D59" t="n">
-        <v>0.120638655665644</v>
+        <v>0.184726133831838</v>
       </c>
       <c r="E59" t="n">
-        <v>11.4583090379009</v>
+        <v>6.60891590678825</v>
       </c>
       <c r="F59" t="n">
-        <v>26.5134398563218</v>
+        <v>12.2129170906203</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I59" t="n">
-        <v>0.918513510998883</v>
+        <v>0.733471659101857</v>
       </c>
       <c r="J59" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -3022,28 +2899,28 @@
         <v>119</v>
       </c>
       <c r="C60" t="n">
-        <v>0.100249023722155</v>
+        <v>0.178674127785297</v>
       </c>
       <c r="D60" t="n">
-        <v>0.120638655665644</v>
+        <v>0.205929503210173</v>
       </c>
       <c r="E60" t="n">
-        <v>11.2908045977011</v>
+        <v>5.74580265095729</v>
       </c>
       <c r="F60" t="n">
-        <v>25.9699565234215</v>
+        <v>9.89537333342662</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I60" t="n">
-        <v>0.918513510998883</v>
+        <v>0.686281428207237</v>
       </c>
       <c r="J60" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -3054,28 +2931,28 @@
         <v>121</v>
       </c>
       <c r="C61" t="n">
-        <v>0.120659906158221</v>
+        <v>0.203922587669778</v>
       </c>
       <c r="D61" t="n">
-        <v>0.142780888953895</v>
+        <v>0.231112266025748</v>
       </c>
       <c r="E61" t="n">
-        <v>9.25342789598109</v>
+        <v>4.94805194805195</v>
       </c>
       <c r="F61" t="n">
-        <v>19.5689585430409</v>
+        <v>7.86747597385955</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I61" t="n">
-        <v>0.845329918451319</v>
+        <v>0.636177004213964</v>
       </c>
       <c r="J61" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
@@ -3086,28 +2963,28 @@
         <v>123</v>
       </c>
       <c r="C62" t="n">
-        <v>0.137240211199119</v>
+        <v>0.231354084211128</v>
       </c>
       <c r="D62" t="n">
-        <v>0.159738606477663</v>
+        <v>0.257902913546831</v>
       </c>
       <c r="E62" t="n">
-        <v>8.04494845360825</v>
+        <v>4.2781954887218</v>
       </c>
       <c r="F62" t="n">
-        <v>15.9774488179155</v>
+        <v>6.26244784037877</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I62" t="n">
-        <v>0.796590108570764</v>
+        <v>0.588543751579921</v>
       </c>
       <c r="J62" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
@@ -3118,28 +2995,28 @@
         <v>125</v>
       </c>
       <c r="C63" t="n">
-        <v>0.149110432986687</v>
+        <v>0.25021607493981</v>
       </c>
       <c r="D63" t="n">
-        <v>0.170755495839594</v>
+        <v>0.274430533804953</v>
       </c>
       <c r="E63" t="n">
-        <v>7.34490566037736</v>
+        <v>3.90246863617968</v>
       </c>
       <c r="F63" t="n">
-        <v>13.9778555611783</v>
+        <v>5.4065988188406</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I63" t="n">
-        <v>0.767625309465474</v>
+        <v>0.56156756962247</v>
       </c>
       <c r="J63" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -3150,28 +3027,28 @@
         <v>127</v>
       </c>
       <c r="C64" t="n">
-        <v>0.15720826780119</v>
+        <v>0.271708804793599</v>
       </c>
       <c r="D64" t="n">
-        <v>0.177171222442611</v>
+        <v>0.293272995650234</v>
       </c>
       <c r="E64" t="n">
-        <v>6.92798573975045</v>
+        <v>3.53755522827688</v>
       </c>
       <c r="F64" t="n">
-        <v>12.818047025374</v>
+        <v>4.6095206258566</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I64" t="n">
-        <v>0.751606818280394</v>
+        <v>0.532727924677202</v>
       </c>
       <c r="J64" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -3182,28 +3059,28 @@
         <v>129</v>
       </c>
       <c r="C65" t="n">
-        <v>0.179083240474479</v>
+        <v>0.341917351004847</v>
       </c>
       <c r="D65" t="n">
-        <v>0.198670469901376</v>
+        <v>0.36328718544265</v>
       </c>
       <c r="E65" t="n">
-        <v>5.99009287925697</v>
+        <v>2.66264383946113</v>
       </c>
       <c r="F65" t="n">
-        <v>10.3023880018557</v>
+        <v>2.85751271682698</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I65" t="n">
-        <v>0.701866681012794</v>
+        <v>0.439749921129024</v>
       </c>
       <c r="J65" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66">
@@ -3214,28 +3091,28 @@
         <v>131</v>
       </c>
       <c r="C66" t="n">
-        <v>0.194237796726968</v>
+        <v>0.376334862732875</v>
       </c>
       <c r="D66" t="n">
-        <v>0.212167439501765</v>
+        <v>0.393704164089776</v>
       </c>
       <c r="E66" t="n">
-        <v>5.46402266288952</v>
+        <v>2.35146600124766</v>
       </c>
       <c r="F66" t="n">
-        <v>8.95374156914419</v>
+        <v>2.29803114571191</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I66" t="n">
-        <v>0.673321264778343</v>
+        <v>0.404829991784197</v>
       </c>
       <c r="J66" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
@@ -3246,28 +3123,28 @@
         <v>133</v>
       </c>
       <c r="C67" t="n">
-        <v>0.211622749515474</v>
+        <v>0.416947534402119</v>
       </c>
       <c r="D67" t="n">
-        <v>0.227654775993919</v>
+        <v>0.42958230817188</v>
       </c>
       <c r="E67" t="n">
-        <v>4.95309278350515</v>
+        <v>2.04900778423418</v>
       </c>
       <c r="F67" t="n">
-        <v>7.69190579917086</v>
+        <v>1.7924615225812</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I67" t="n">
-        <v>0.642723234149787</v>
+        <v>0.366953612833506</v>
       </c>
       <c r="J67" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68">
@@ -3278,28 +3155,28 @@
         <v>135</v>
       </c>
       <c r="C68" t="n">
-        <v>0.269336616071375</v>
+        <v>0.602320700736056</v>
       </c>
       <c r="D68" t="n">
-        <v>0.285416414045785</v>
+        <v>0.611310561941071</v>
       </c>
       <c r="E68" t="n">
-        <v>3.72809430255403</v>
+        <v>1.16964285714286</v>
       </c>
       <c r="F68" t="n">
-        <v>4.89048920547602</v>
+        <v>0.592968283535925</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I68" t="n">
-        <v>0.54452105461125</v>
+        <v>0.213738100606262</v>
       </c>
       <c r="J68" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69">
@@ -3310,124 +3187,28 @@
         <v>137</v>
       </c>
       <c r="C69" t="n">
-        <v>0.298186794099356</v>
+        <v>0.627314398715263</v>
       </c>
       <c r="D69" t="n">
-        <v>0.311342093839034</v>
+        <v>0.627314398715263</v>
       </c>
       <c r="E69" t="n">
-        <v>3.29240174672489</v>
+        <v>1.08817733990148</v>
       </c>
       <c r="F69" t="n">
-        <v>3.98392188430328</v>
+        <v>0.507425179479766</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I69" t="n">
-        <v>0.506762158192706</v>
+        <v>0.202514744009264</v>
       </c>
       <c r="J69" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>138</v>
-      </c>
-      <c r="B70" t="s">
-        <v>139</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.332748090762633</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0.342392962958651</v>
-      </c>
-      <c r="E70" t="n">
-        <v>2.8689178818112</v>
-      </c>
-      <c r="F70" t="n">
-        <v>3.15686990578299</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.465475169753157</v>
-      </c>
-      <c r="J70" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>140</v>
-      </c>
-      <c r="B71" t="s">
-        <v>141</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.499198521700123</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0.506329929152982</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1.63768382352941</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1.137783167262</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0.295566400715425</v>
-      </c>
-      <c r="J71" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>142</v>
-      </c>
-      <c r="B72" t="s">
-        <v>143</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.522993828733475</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0.522993828733475</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1.52362068965517</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.987589013341955</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.28150343572701</v>
-      </c>
-      <c r="J72" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3449,7 +3230,7 @@
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="60.71" hidden="0" customWidth="1"/>
   </cols>
@@ -3488,386 +3269,322 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0000370514344902947</v>
+        <v>0.0000690248633798375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000444617213883536</v>
+        <v>0.000690248633798376</v>
       </c>
       <c r="E2" t="n">
-        <v>332.733333333333</v>
+        <v>221.8</v>
       </c>
       <c r="F2" t="n">
-        <v>3394.94590766807</v>
+        <v>2125.07551027874</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35201372708482</v>
+        <v>3.1609944442822</v>
       </c>
       <c r="J2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0014992198216207</v>
+        <v>0.00479070309341298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00599687928648278</v>
+        <v>0.0239535154670649</v>
       </c>
       <c r="E3" t="n">
-        <v>999.5</v>
+        <v>259.493506493507</v>
       </c>
       <c r="F3" t="n">
-        <v>6499.55901988972</v>
+        <v>1385.97508325908</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I3" t="n">
-        <v>2.22207469315689</v>
+        <v>1.62063073962279</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0014992198216207</v>
+        <v>0.0166797975569069</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00599687928648278</v>
+        <v>0.0396583229023702</v>
       </c>
       <c r="E4" t="n">
-        <v>999.5</v>
+        <v>69.5156794425087</v>
       </c>
       <c r="F4" t="n">
-        <v>6499.55901988972</v>
+        <v>284.566397512524</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.22207469315689</v>
+        <v>1.40166565547733</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00329582567641046</v>
+        <v>0.0198291614511851</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00988747702923139</v>
+        <v>0.0396583229023702</v>
       </c>
       <c r="E5" t="n">
-        <v>399.68</v>
+        <v>58.1428571428571</v>
       </c>
       <c r="F5" t="n">
-        <v>2284.21059157039</v>
+        <v>227.954980151296</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I5" t="n">
-        <v>2.00491451245403</v>
+        <v>1.40166565547733</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00766814018589269</v>
+        <v>0.013877379587164</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0184035364461425</v>
+        <v>0.0396583229023702</v>
       </c>
       <c r="E6" t="n">
-        <v>20.9989247311828</v>
+        <v>13.9978494623656</v>
       </c>
       <c r="F6" t="n">
-        <v>102.279067321024</v>
+        <v>59.8757329376123</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7350987144106</v>
+        <v>1.40166565547733</v>
       </c>
       <c r="J6" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0149082847993736</v>
+        <v>0.0280542928380034</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0298165695987473</v>
+        <v>0.0467571547300056</v>
       </c>
       <c r="E7" t="n">
-        <v>81.4081632653061</v>
+        <v>40.6571428571429</v>
       </c>
       <c r="F7" t="n">
-        <v>342.389562344484</v>
+        <v>145.292919316992</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I7" t="n">
-        <v>1.52554232366078</v>
+        <v>1.33015192442753</v>
       </c>
       <c r="J7" t="s">
-        <v>23</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0348860358299779</v>
+        <v>0.0462444344043176</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0476794283634042</v>
+        <v>0.0526614728585067</v>
       </c>
       <c r="E8" t="n">
-        <v>33.9777777777778</v>
+        <v>24.2673992673993</v>
       </c>
       <c r="F8" t="n">
-        <v>114.018163662715</v>
+        <v>74.5934754816134</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I8" t="n">
-        <v>1.32166896006537</v>
+        <v>1.27850699852701</v>
       </c>
       <c r="J8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0357595712725532</v>
+        <v>0.047395325572656</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0476794283634042</v>
+        <v>0.0526614728585067</v>
       </c>
       <c r="E9" t="n">
-        <v>33.1233333333333</v>
+        <v>23.6571428571429</v>
       </c>
       <c r="F9" t="n">
-        <v>110.331747088977</v>
+        <v>72.1361092632249</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I9" t="n">
-        <v>1.32166896006537</v>
+        <v>1.27850699852701</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0357595712725532</v>
+        <v>0.047395325572656</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0476794283634042</v>
+        <v>0.0526614728585067</v>
       </c>
       <c r="E10" t="n">
-        <v>33.1233333333333</v>
+        <v>23.6571428571429</v>
       </c>
       <c r="F10" t="n">
-        <v>110.331747088977</v>
+        <v>72.1361092632249</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I10" t="n">
-        <v>1.32166896006537</v>
+        <v>1.27850699852701</v>
       </c>
       <c r="J10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0585267307609904</v>
+        <v>0.193707111727762</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0702320769131885</v>
+        <v>0.193707111727762</v>
       </c>
       <c r="E11" t="n">
-        <v>19.894472361809</v>
+        <v>5.24582210242588</v>
       </c>
       <c r="F11" t="n">
-        <v>56.4659177521415</v>
+        <v>8.61053433442562</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>1.15346448837426</v>
+        <v>0.712854434379359</v>
       </c>
       <c r="J11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12" t="s">
-        <v>162</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.0670542795241716</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.0731501231172781</v>
-      </c>
-      <c r="E12" t="n">
-        <v>17.2620087336245</v>
-      </c>
-      <c r="F12" t="n">
-        <v>46.6463122182289</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.13578493858707</v>
-      </c>
-      <c r="J12" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.149110432986687</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.149110432986687</v>
-      </c>
-      <c r="E13" t="n">
-        <v>7.34490566037736</v>
-      </c>
-      <c r="F13" t="n">
-        <v>13.9778555611783</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.826491968686295</v>
-      </c>
-      <c r="J13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3889,7 +3606,7 @@
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="60.71" hidden="0" customWidth="1"/>
   </cols>
@@ -3928,482 +3645,386 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00336051193499512</v>
+        <v>0.0253193180336771</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0504076790249268</v>
+        <v>0.0716630861195948</v>
       </c>
       <c r="E2" t="n">
-        <v>32.3848684210526</v>
+        <v>45.1904761904762</v>
       </c>
       <c r="F2" t="n">
-        <v>184.453262983703</v>
+        <v>166.12866893112</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I2" t="n">
-        <v>1.29750329879023</v>
+        <v>1.14470449318566</v>
       </c>
       <c r="J2" t="s">
-        <v>166</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0190492685407353</v>
+        <v>0.0264922734714403</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0563464267966121</v>
+        <v>0.0716630861195948</v>
       </c>
       <c r="E3" t="n">
-        <v>63.2730158730159</v>
+        <v>43.1298701298701</v>
       </c>
       <c r="F3" t="n">
-        <v>250.607115446019</v>
+        <v>156.600338426129</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I3" t="n">
-        <v>1.24913361948864</v>
+        <v>1.14470449318566</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0199347325407438</v>
+        <v>0.0307825507393775</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0563464267966121</v>
+        <v>0.0716630861195948</v>
       </c>
       <c r="E4" t="n">
-        <v>60.3878787878788</v>
+        <v>36.948051948052</v>
       </c>
       <c r="F4" t="n">
-        <v>236.436161492859</v>
+        <v>128.609048349639</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I4" t="n">
-        <v>1.24913361948864</v>
+        <v>1.14470449318566</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0267011909686245</v>
+        <v>0.00614717984176483</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0563464267966121</v>
+        <v>0.0716630861195948</v>
       </c>
       <c r="E5" t="n">
-        <v>44.7303370786517</v>
+        <v>21.5877192982456</v>
       </c>
       <c r="F5" t="n">
-        <v>162.060118437595</v>
+        <v>109.919525867581</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.166666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="I5" t="n">
-        <v>1.24913361948864</v>
+        <v>1.14470449318566</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0269944994833615</v>
+        <v>0.0354439777386331</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0563464267966121</v>
+        <v>0.0716630861195948</v>
       </c>
       <c r="E6" t="n">
-        <v>44.2311111111111</v>
+        <v>31.9470304975923</v>
       </c>
       <c r="F6" t="n">
-        <v>159.76817645418</v>
+        <v>106.696753821913</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I6" t="n">
-        <v>1.24913361948864</v>
+        <v>1.14470449318566</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0171549810602662</v>
+        <v>0.0358315430597974</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0563464267966121</v>
+        <v>0.0716630861195948</v>
       </c>
       <c r="E7" t="n">
-        <v>8.72470817120623</v>
+        <v>31.5904761904762</v>
       </c>
       <c r="F7" t="n">
-        <v>35.4700105957832</v>
+        <v>105.162379101859</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="I7" t="n">
-        <v>1.24913361948864</v>
+        <v>1.14470449318566</v>
       </c>
       <c r="J7" t="s">
-        <v>177</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0300514276248598</v>
+        <v>0.0526522433401142</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0563464267966121</v>
+        <v>0.0902609885830529</v>
       </c>
       <c r="E8" t="n">
-        <v>9.9900314795383</v>
+        <v>6.65932144106331</v>
       </c>
       <c r="F8" t="n">
-        <v>35.0135129879438</v>
+        <v>19.6053515331692</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1.24913361948864</v>
+        <v>1.04449991418155</v>
       </c>
       <c r="J8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0176875187806402</v>
+        <v>0.069408326255472</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0563464267966121</v>
+        <v>0.104112489383208</v>
       </c>
       <c r="E9" t="n">
-        <v>8.61712361712362</v>
+        <v>15.9020866773676</v>
       </c>
       <c r="F9" t="n">
-        <v>34.7691979742289</v>
+        <v>42.422766986769</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="I9" t="n">
-        <v>1.24913361948864</v>
+        <v>0.982497169193983</v>
       </c>
       <c r="J9" t="s">
-        <v>177</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C10" t="n">
-        <v>0.052518881698076</v>
+        <v>0.0906068463642597</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0875314694967932</v>
+        <v>0.12080912848568</v>
       </c>
       <c r="E10" t="n">
-        <v>22.2651685393258</v>
+        <v>12.0103343465046</v>
       </c>
       <c r="F10" t="n">
-        <v>65.6061564818719</v>
+        <v>28.8395211186174</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I10" t="n">
-        <v>1.05783578044384</v>
+        <v>0.917900248652175</v>
       </c>
       <c r="J10" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0596674758349562</v>
+        <v>0.120361565278333</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0895012137524342</v>
+        <v>0.144433878334</v>
       </c>
       <c r="E11" t="n">
-        <v>19.4985221674877</v>
+        <v>8.86660657954033</v>
       </c>
       <c r="F11" t="n">
-        <v>54.9657139453661</v>
+        <v>18.7728673115885</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>1.04817107504822</v>
+        <v>0.840330926933831</v>
       </c>
       <c r="J11" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0861453452027456</v>
+        <v>0.195695105113042</v>
       </c>
       <c r="D12" t="n">
-        <v>0.108460235238325</v>
+        <v>0.199156288826046</v>
       </c>
       <c r="E12" t="n">
-        <v>13.2639730639731</v>
+        <v>2.90633608815427</v>
       </c>
       <c r="F12" t="n">
-        <v>32.5195394025965</v>
+        <v>4.74080792019254</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0.166666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="I12" t="n">
-        <v>0.964729457962561</v>
+        <v>0.700805975173172</v>
       </c>
       <c r="J12" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0916979944934551</v>
+        <v>0.199156288826046</v>
       </c>
       <c r="D13" t="n">
-        <v>0.108460235238325</v>
+        <v>0.199156288826046</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4145110410095</v>
+        <v>2.87051282051282</v>
       </c>
       <c r="F13" t="n">
-        <v>29.6614297251681</v>
+        <v>4.63204719436136</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.166666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="I13" t="n">
-        <v>0.964729457962561</v>
+        <v>0.700805975173172</v>
       </c>
       <c r="J13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>190</v>
-      </c>
-      <c r="B14" t="s">
-        <v>191</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.101347479208919</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.108460235238325</v>
-      </c>
-      <c r="E14" t="n">
-        <v>11.1602272727273</v>
-      </c>
-      <c r="F14" t="n">
-        <v>25.5479953811899</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.964729457962561</v>
-      </c>
-      <c r="J14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" t="s">
-        <v>193</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.106276709803964</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.108460235238325</v>
-      </c>
-      <c r="E15" t="n">
-        <v>10.6075675675676</v>
-      </c>
-      <c r="F15" t="n">
-        <v>23.779080918829</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.964729457962561</v>
-      </c>
-      <c r="J15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>194</v>
-      </c>
-      <c r="B16" t="s">
-        <v>195</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.108460235238325</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.108460235238325</v>
-      </c>
-      <c r="E16" t="n">
-        <v>10.378835978836</v>
-      </c>
-      <c r="F16" t="n">
-        <v>23.0552521972299</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.964729457962561</v>
-      </c>
-      <c r="J16" t="s">
-        <v>28</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -4425,7 +4046,7 @@
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="60.71" hidden="0" customWidth="1"/>
   </cols>
@@ -4464,31 +4085,31 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000283828364571552</v>
+        <v>0.0307825507393775</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00879867930171812</v>
+        <v>0.106895406468325</v>
       </c>
       <c r="E2" t="n">
-        <v>115.744186046512</v>
+        <v>36.948051948052</v>
       </c>
       <c r="F2" t="n">
-        <v>945.29907031098</v>
+        <v>128.609048349639</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I2" t="n">
-        <v>2.05558251137495</v>
+        <v>0.971040956983196</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -4496,31 +4117,31 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000854709539721723</v>
+        <v>0.0346684381611494</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0118785571704819</v>
+        <v>0.106895406468325</v>
       </c>
       <c r="E3" t="n">
-        <v>65.705298013245</v>
+        <v>32.6847290640394</v>
       </c>
       <c r="F3" t="n">
-        <v>464.191429653511</v>
+        <v>109.883626356627</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I3" t="n">
-        <v>1.92523630775148</v>
+        <v>0.971040956983196</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -4528,31 +4149,31 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0014392276912047</v>
+        <v>0.0362189721188044</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0118785571704819</v>
+        <v>0.106895406468325</v>
       </c>
       <c r="E4" t="n">
-        <v>50.246192893401</v>
+        <v>31.2417582417582</v>
       </c>
       <c r="F4" t="n">
-        <v>328.793431531832</v>
+        <v>103.665533856838</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I4" t="n">
-        <v>1.92523630775148</v>
+        <v>0.971040956983196</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
@@ -4560,31 +4181,31 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00188315349863043</v>
+        <v>0.0393135041520565</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0118785571704819</v>
+        <v>0.106895406468325</v>
       </c>
       <c r="E5" t="n">
-        <v>43.7345132743363</v>
+        <v>28.7056277056277</v>
       </c>
       <c r="F5" t="n">
-        <v>274.425652536979</v>
+        <v>92.8967850071638</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I5" t="n">
-        <v>1.92523630775148</v>
+        <v>0.971040956983196</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -4592,31 +4213,31 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00191589631781967</v>
+        <v>0.0393135041520565</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0118785571704819</v>
+        <v>0.106895406468325</v>
       </c>
       <c r="E6" t="n">
-        <v>43.3464912280702</v>
+        <v>28.7056277056277</v>
       </c>
       <c r="F6" t="n">
-        <v>271.243690750337</v>
+        <v>92.8967850071638</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I6" t="n">
-        <v>1.92523630775148</v>
+        <v>0.971040956983196</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
@@ -4624,63 +4245,63 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="B7" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0038505575448098</v>
+        <v>0.0400857774256217</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0198945473148506</v>
+        <v>0.106895406468325</v>
       </c>
       <c r="E7" t="n">
-        <v>30.1656441717791</v>
+        <v>28.1343705799151</v>
       </c>
       <c r="F7" t="n">
-        <v>167.707024685575</v>
+        <v>90.5007775576607</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I7" t="n">
-        <v>1.70126593844266</v>
+        <v>0.971040956983196</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B8" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0044953059420577</v>
+        <v>0.0538941184428828</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0199077834576841</v>
+        <v>0.108794467476642</v>
       </c>
       <c r="E8" t="n">
-        <v>27.8201133144476</v>
+        <v>20.70385818561</v>
       </c>
       <c r="F8" t="n">
-        <v>150.359965971438</v>
+        <v>60.4704610187662</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I8" t="n">
-        <v>1.70097709184023</v>
+        <v>0.963393189246826</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
@@ -4688,770 +4309,290 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B9" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0231757383378881</v>
+        <v>0.0595960981777748</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0591101427146882</v>
+        <v>0.108794467476642</v>
       </c>
       <c r="E9" t="n">
-        <v>51.7324675324675</v>
+        <v>18.6466165413534</v>
       </c>
       <c r="F9" t="n">
-        <v>194.754598138502</v>
+        <v>52.5865385804282</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I9" t="n">
-        <v>1.22833799209542</v>
+        <v>0.963393189246826</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B10" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02523354305099</v>
+        <v>0.0761488191827759</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0591101427146882</v>
+        <v>0.108794467476642</v>
       </c>
       <c r="E10" t="n">
-        <v>47.4047619047619</v>
+        <v>14.4285714285714</v>
       </c>
       <c r="F10" t="n">
-        <v>174.429665770154</v>
+        <v>37.1545194755331</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I10" t="n">
-        <v>1.22833799209542</v>
+        <v>0.963393189246826</v>
       </c>
       <c r="J10" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B11" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C11" t="n">
-        <v>0.025527220063161</v>
+        <v>0.076895119183702</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0591101427146882</v>
+        <v>0.108794467476642</v>
       </c>
       <c r="E11" t="n">
-        <v>46.8447058823529</v>
+        <v>14.2813852813853</v>
       </c>
       <c r="F11" t="n">
-        <v>171.826846938568</v>
+        <v>36.6362215228568</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>1.22833799209542</v>
+        <v>0.963393189246826</v>
       </c>
       <c r="J11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B12" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0272877343434333</v>
+        <v>0.0809903476493452</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0591101427146882</v>
+        <v>0.108794467476642</v>
       </c>
       <c r="E12" t="n">
-        <v>43.7428571428571</v>
+        <v>13.5222146274778</v>
       </c>
       <c r="F12" t="n">
-        <v>157.531937452816</v>
+        <v>33.9870763057985</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I12" t="n">
-        <v>1.22833799209542</v>
+        <v>0.963393189246826</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B13" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0290455975649231</v>
+        <v>0.0876573461487165</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0591101427146882</v>
+        <v>0.108794467476642</v>
       </c>
       <c r="E13" t="n">
-        <v>41.0247422680412</v>
+        <v>12.4386406544997</v>
       </c>
       <c r="F13" t="n">
-        <v>145.181982637693</v>
+        <v>30.2796299619726</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I13" t="n">
-        <v>1.22833799209542</v>
+        <v>0.963393189246826</v>
       </c>
       <c r="J13" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B14" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0296309633944118</v>
+        <v>0.0883955048247714</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0591101427146882</v>
+        <v>0.108794467476642</v>
       </c>
       <c r="E14" t="n">
-        <v>40.1919191919192</v>
+        <v>12.3287585776669</v>
       </c>
       <c r="F14" t="n">
-        <v>141.432767389918</v>
+        <v>29.9087565966534</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I14" t="n">
-        <v>1.22833799209542</v>
+        <v>0.963393189246826</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0296309633944118</v>
+        <v>0.123931244775128</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0591101427146882</v>
+        <v>0.141635708314432</v>
       </c>
       <c r="E15" t="n">
-        <v>40.1919191919192</v>
+        <v>8.5910878112713</v>
       </c>
       <c r="F15" t="n">
-        <v>141.432767389918</v>
+        <v>17.9384348623992</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I15" t="n">
-        <v>1.22833799209542</v>
+        <v>0.84882724121637</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C16" t="n">
-        <v>0.030216035137483</v>
+        <v>0.13350614314527</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0591101427146882</v>
+        <v>0.142406552688288</v>
       </c>
       <c r="E16" t="n">
-        <v>39.3920792079208</v>
+        <v>7.92493946731235</v>
       </c>
       <c r="F16" t="n">
-        <v>137.847953827989</v>
+        <v>15.9577198159978</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I16" t="n">
-        <v>1.22833799209542</v>
+        <v>0.846470026633917</v>
       </c>
       <c r="J16" t="s">
-        <v>225</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0305084607559681</v>
+        <v>0.191716729420111</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0591101427146882</v>
+        <v>0.191716729420111</v>
       </c>
       <c r="E17" t="n">
-        <v>39.0039215686275</v>
+        <v>5.30752453653217</v>
       </c>
       <c r="F17" t="n">
-        <v>136.113983347048</v>
+        <v>8.76663127972961</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.166666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="I17" t="n">
-        <v>1.22833799209542</v>
+        <v>0.717339988437364</v>
       </c>
       <c r="J17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>228</v>
-      </c>
-      <c r="B18" t="s">
-        <v>229</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.040697170601244</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.0742124875669744</v>
-      </c>
-      <c r="E18" t="n">
-        <v>28.9883211678832</v>
-      </c>
-      <c r="F18" t="n">
-        <v>92.8089136026139</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.12952301082445</v>
-      </c>
-      <c r="J18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>230</v>
-      </c>
-      <c r="B19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.0444587497780508</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.0765678468399763</v>
-      </c>
-      <c r="E19" t="n">
-        <v>26.4586666666667</v>
-      </c>
-      <c r="F19" t="n">
-        <v>82.3709488470273</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.11595356550453</v>
-      </c>
-      <c r="J19" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B20" t="s">
-        <v>233</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.0556698218369758</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.085553985891766</v>
-      </c>
-      <c r="E20" t="n">
-        <v>20.957671957672</v>
-      </c>
-      <c r="F20" t="n">
-        <v>60.5324018123073</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.06775975221903</v>
-      </c>
-      <c r="J20" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>234</v>
-      </c>
-      <c r="B21" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.0576704153745895</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.085553985891766</v>
-      </c>
-      <c r="E21" t="n">
-        <v>20.2020408163265</v>
-      </c>
-      <c r="F21" t="n">
-        <v>57.6366440405093</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.06775975221903</v>
-      </c>
-      <c r="J21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>236</v>
-      </c>
-      <c r="B22" t="s">
-        <v>237</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.0579559259266802</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.085553985891766</v>
-      </c>
-      <c r="E22" t="n">
-        <v>20.0984771573604</v>
-      </c>
-      <c r="F22" t="n">
-        <v>57.2419191817422</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.06775975221903</v>
-      </c>
-      <c r="J22" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>238</v>
-      </c>
-      <c r="B23" t="s">
-        <v>239</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.0613764336739604</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.0864849747223987</v>
-      </c>
-      <c r="E23" t="n">
-        <v>18.933014354067</v>
-      </c>
-      <c r="F23" t="n">
-        <v>52.836918536863</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.06305933718208</v>
-      </c>
-      <c r="J23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>240</v>
-      </c>
-      <c r="B24" t="s">
-        <v>241</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.071011717989692</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0957114459861066</v>
-      </c>
-      <c r="E24" t="n">
-        <v>16.2559670781893</v>
-      </c>
-      <c r="F24" t="n">
-        <v>42.9955759555716</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.01903612250151</v>
-      </c>
-      <c r="J24" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>242</v>
-      </c>
-      <c r="B25" t="s">
-        <v>243</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.0763601439895147</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0964265559742815</v>
-      </c>
-      <c r="E25" t="n">
-        <v>15.0625954198473</v>
-      </c>
-      <c r="F25" t="n">
-        <v>38.7454297644861</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.0158033444703</v>
-      </c>
-      <c r="J25" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>244</v>
-      </c>
-      <c r="B26" t="s">
-        <v>245</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.0777633515921625</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0964265559742815</v>
-      </c>
-      <c r="E26" t="n">
-        <v>14.7767790262172</v>
-      </c>
-      <c r="F26" t="n">
-        <v>37.7411499252725</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.0158033444703</v>
-      </c>
-      <c r="J26" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>246</v>
-      </c>
-      <c r="B27" t="s">
-        <v>247</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.0850314280432312</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.100504471083851</v>
-      </c>
-      <c r="E27" t="n">
-        <v>13.4477815699659</v>
-      </c>
-      <c r="F27" t="n">
-        <v>33.1452091552853</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.997814617608139</v>
-      </c>
-      <c r="J27" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>248</v>
-      </c>
-      <c r="B28" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.0875361522343221</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.100504471083851</v>
-      </c>
-      <c r="E28" t="n">
-        <v>13.041059602649</v>
-      </c>
-      <c r="F28" t="n">
-        <v>31.7641532471192</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.997814617608139</v>
-      </c>
-      <c r="J28" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>250</v>
-      </c>
-      <c r="B29" t="s">
-        <v>251</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.103814918648103</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.114937945646114</v>
-      </c>
-      <c r="E29" t="n">
-        <v>10.8770083102493</v>
-      </c>
-      <c r="F29" t="n">
-        <v>24.6380074459929</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.939536569535102</v>
-      </c>
-      <c r="J29" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>252</v>
-      </c>
-      <c r="B30" t="s">
-        <v>195</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.108460235238325</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.115940251461658</v>
-      </c>
-      <c r="E30" t="n">
-        <v>10.378835978836</v>
-      </c>
-      <c r="F30" t="n">
-        <v>23.0552521972299</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.935765762027245</v>
-      </c>
-      <c r="J30" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>253</v>
-      </c>
-      <c r="B31" t="s">
-        <v>254</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.132720144342348</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.13714414915376</v>
-      </c>
-      <c r="E31" t="n">
-        <v>8.34444444444444</v>
-      </c>
-      <c r="F31" t="n">
-        <v>16.8517102410345</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.862822715543504</v>
-      </c>
-      <c r="J31" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>255</v>
-      </c>
-      <c r="B32" t="s">
-        <v>256</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.147535645706635</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.147535645706635</v>
-      </c>
-      <c r="E32" t="n">
-        <v>7.43129770992366</v>
-      </c>
-      <c r="F32" t="n">
-        <v>14.2211664253922</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.831103038238941</v>
-      </c>
-      <c r="J32" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
